--- a/output/pdf_financials_xlsx/FDR.xlsx
+++ b/output/pdf_financials_xlsx/FDR.xlsx
@@ -3040,10 +3040,10 @@
         <v>0</v>
       </c>
       <c r="F103" s="3" t="n">
-        <v>0</v>
+        <v>-0.08558399999999999</v>
       </c>
       <c r="G103" s="3" t="n">
-        <v>0</v>
+        <v>-0.909316</v>
       </c>
     </row>
     <row r="104">
@@ -3115,10 +3115,10 @@
         <v>0.872475</v>
       </c>
       <c r="F106" s="3" t="n">
-        <v>-0.7105</v>
+        <v>-0.796084</v>
       </c>
       <c r="G106" s="3" t="n">
-        <v>0.267731</v>
+        <v>-0.641585</v>
       </c>
     </row>
     <row r="107">
@@ -4082,7 +4082,11 @@
           <t>Prepaids and deposits</t>
         </is>
       </c>
-      <c r="D5" t="inlineStr"/>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>PrepaidAssets</t>
+        </is>
+      </c>
       <c r="E5" t="inlineStr">
         <is>
           <t>-</t>
@@ -4210,7 +4214,11 @@
           <t>Prepaids and deposits (note 4)</t>
         </is>
       </c>
-      <c r="D8" t="inlineStr"/>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>PrepaidAssets</t>
+        </is>
+      </c>
       <c r="E8" t="inlineStr">
         <is>
           <t>-</t>
@@ -4828,7 +4836,11 @@
           <t>Prepaids and deposits</t>
         </is>
       </c>
-      <c r="D22" t="inlineStr"/>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>PrepaidAssets</t>
+        </is>
+      </c>
       <c r="E22" t="inlineStr">
         <is>
           <t>-</t>
@@ -5848,7 +5860,11 @@
           <t>Prepaids and deposits 14,295</t>
         </is>
       </c>
-      <c r="D44" t="inlineStr"/>
+      <c r="D44" t="inlineStr">
+        <is>
+          <t>PrepaidAssets</t>
+        </is>
+      </c>
       <c r="E44" t="inlineStr">
         <is>
           <t>-</t>
@@ -7002,7 +7018,11 @@
           <t>Prepaids and deposits</t>
         </is>
       </c>
-      <c r="D69" t="inlineStr"/>
+      <c r="D69" t="inlineStr">
+        <is>
+          <t>ChangeInPrepaidAssets</t>
+        </is>
+      </c>
       <c r="E69" t="inlineStr">
         <is>
           <t>-</t>

--- a/output/pdf_financials_xlsx/FDR.xlsx
+++ b/output/pdf_financials_xlsx/FDR.xlsx
@@ -699,22 +699,22 @@
         </is>
       </c>
       <c r="B12" s="3" t="n">
-        <v>0</v>
+        <v>-0.026375</v>
       </c>
       <c r="C12" s="3" t="n">
         <v>0</v>
       </c>
       <c r="D12" s="3" t="n">
-        <v>0</v>
+        <v>0.016903</v>
       </c>
       <c r="E12" s="3" t="n">
-        <v>0</v>
+        <v>0.04075</v>
       </c>
       <c r="F12" s="3" t="n">
-        <v>0</v>
+        <v>0.228167</v>
       </c>
       <c r="G12" s="3" t="n">
-        <v>0</v>
+        <v>0.713803</v>
       </c>
     </row>
     <row r="13">
@@ -1100,22 +1100,22 @@
         </is>
       </c>
       <c r="B27" s="3" t="n">
-        <v>-0.422253</v>
+        <v>-0.395878</v>
       </c>
       <c r="C27" s="3" t="n">
         <v>-0.106049</v>
       </c>
       <c r="D27" s="3" t="n">
-        <v>-0.485772</v>
+        <v>-0.502675</v>
       </c>
       <c r="E27" s="3" t="n">
-        <v>-1.862254</v>
+        <v>-1.903004</v>
       </c>
       <c r="F27" s="3" t="n">
-        <v>-7.738457</v>
+        <v>-7.966624</v>
       </c>
       <c r="G27" s="3" t="n">
-        <v>-10.585128</v>
+        <v>-11.298931</v>
       </c>
     </row>
     <row r="28">
@@ -1150,22 +1150,22 @@
         </is>
       </c>
       <c r="B29" s="3" t="n">
-        <v>-0.422253</v>
+        <v>-0.395878</v>
       </c>
       <c r="C29" s="3" t="n">
         <v>-0.106049</v>
       </c>
       <c r="D29" s="3" t="n">
-        <v>-0.485772</v>
+        <v>-0.502675</v>
       </c>
       <c r="E29" s="3" t="n">
-        <v>-1.862254</v>
+        <v>-1.903004</v>
       </c>
       <c r="F29" s="3" t="n">
-        <v>-7.738457</v>
+        <v>-7.966624</v>
       </c>
       <c r="G29" s="3" t="n">
-        <v>-10.585128</v>
+        <v>-11.298931</v>
       </c>
     </row>
     <row r="30">
@@ -1175,7 +1175,7 @@
         </is>
       </c>
       <c r="B30" s="3" t="n">
-        <v>-66.62863851320967</v>
+        <v>-62.46684371060102</v>
       </c>
       <c r="C30" s="3" t="n">
         <v>-151498.5714285714</v>
@@ -1279,16 +1279,16 @@
         <v>0.002616</v>
       </c>
       <c r="D34" s="3" t="n">
-        <v>0</v>
+        <v>0.96959</v>
       </c>
       <c r="E34" s="3" t="n">
-        <v>0</v>
+        <v>2.028169</v>
       </c>
       <c r="F34" s="3" t="n">
-        <v>0</v>
+        <v>4.800069</v>
       </c>
       <c r="G34" s="3" t="n">
-        <v>0</v>
+        <v>25.746648</v>
       </c>
     </row>
     <row r="35">
@@ -1329,16 +1329,16 @@
         <v>0.002616</v>
       </c>
       <c r="D36" s="3" t="n">
-        <v>0</v>
+        <v>0.96959</v>
       </c>
       <c r="E36" s="3" t="n">
-        <v>0</v>
+        <v>2.028169</v>
       </c>
       <c r="F36" s="3" t="n">
-        <v>0</v>
+        <v>4.800069</v>
       </c>
       <c r="G36" s="3" t="n">
-        <v>0</v>
+        <v>25.746648</v>
       </c>
     </row>
     <row r="37">
@@ -1629,16 +1629,16 @@
         <v>0.003059</v>
       </c>
       <c r="D48" s="3" t="n">
-        <v>1.268683</v>
+        <v>0.299093</v>
       </c>
       <c r="E48" s="3" t="n">
-        <v>2.310447</v>
+        <v>0.282278</v>
       </c>
       <c r="F48" s="3" t="n">
-        <v>5.082325</v>
+        <v>0.282256</v>
       </c>
       <c r="G48" s="3" t="n">
-        <v>26.106784</v>
+        <v>0.360136</v>
       </c>
     </row>
     <row r="49">
@@ -3988,7 +3988,7 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -4746,7 +4746,7 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
@@ -5400,7 +5400,7 @@
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
@@ -5766,7 +5766,7 @@
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
@@ -10308,7 +10308,7 @@
       </c>
       <c r="D141" t="inlineStr">
         <is>
-          <t>InterestIncome</t>
+          <t>InterestIncomeNonOperating</t>
         </is>
       </c>
       <c r="E141" t="inlineStr">
@@ -10778,7 +10778,7 @@
       </c>
       <c r="D151" t="inlineStr">
         <is>
-          <t>TotalExpenses</t>
+          <t>OperatingExpense</t>
         </is>
       </c>
       <c r="E151" t="inlineStr">
@@ -10797,10 +10797,10 @@
         </is>
       </c>
       <c r="H151" s="5" t="n">
-        <v>-1.031904</v>
+        <v>1.031904</v>
       </c>
       <c r="I151" s="5" t="n">
-        <v>-2.596099</v>
+        <v>2.596099</v>
       </c>
       <c r="J151" t="inlineStr">
         <is>
@@ -10826,7 +10826,7 @@
       </c>
       <c r="D152" t="inlineStr">
         <is>
-          <t>InterestIncome</t>
+          <t>InterestIncomeNonOperating</t>
         </is>
       </c>
       <c r="E152" t="inlineStr">
@@ -11892,7 +11892,7 @@
       </c>
       <c r="D175" t="inlineStr">
         <is>
-          <t>InterestIncome</t>
+          <t>InterestIncomeNonOperating</t>
         </is>
       </c>
       <c r="E175" s="5" t="n">

--- a/output/pdf_financials_xlsx/FDR.xlsx
+++ b/output/pdf_financials_xlsx/FDR.xlsx
@@ -3034,7 +3034,7 @@
         <v>0.002883</v>
       </c>
       <c r="D103" s="3" t="n">
-        <v>0</v>
+        <v>-0.064042</v>
       </c>
       <c r="E103" s="3" t="n">
         <v>0</v>
@@ -3109,7 +3109,7 @@
         <v>0.01971</v>
       </c>
       <c r="D106" s="3" t="n">
-        <v>-0.165085</v>
+        <v>-0.229127</v>
       </c>
       <c r="E106" s="3" t="n">
         <v>0.872475</v>
@@ -3234,7 +3234,7 @@
         <v>0</v>
       </c>
       <c r="D111" s="3" t="n">
-        <v>0</v>
+        <v>-0.06283999999999999</v>
       </c>
       <c r="E111" s="3" t="n">
         <v>0</v>
@@ -3821,7 +3821,7 @@
         <v>0</v>
       </c>
       <c r="D134" s="3" t="n">
-        <v>0</v>
+        <v>-0.06283999999999999</v>
       </c>
       <c r="E134" s="3" t="n">
         <v>0</v>
@@ -3846,7 +3846,7 @@
         <v>-0.07709000000000001</v>
       </c>
       <c r="D135" s="3" t="n">
-        <v>-0.952853</v>
+        <v>-1.015693</v>
       </c>
       <c r="E135" s="3" t="n">
         <v>-0.78147</v>
@@ -3869,7 +3869,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J190"/>
+  <dimension ref="A1:J222"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -9048,31 +9048,25 @@
           <t>cash_flow</t>
         </is>
       </c>
-      <c r="B114" t="inlineStr">
-        <is>
-          <t>Operating activities</t>
-        </is>
-      </c>
+      <c r="B114" t="inlineStr"/>
       <c r="C114" t="inlineStr">
         <is>
-          <t>Net loss for the year</t>
-        </is>
-      </c>
-      <c r="D114" t="inlineStr">
-        <is>
-          <t>NetIncomeFromContinuingOperations</t>
-        </is>
-      </c>
-      <c r="E114" s="5" t="n">
-        <v>-0.422428</v>
-      </c>
-      <c r="F114" s="5" t="n">
-        <v>-0.106049</v>
-      </c>
-      <c r="G114" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>For the years ended August 31 August</t>
+        </is>
+      </c>
+      <c r="D114" t="inlineStr"/>
+      <c r="E114" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F114" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G114" s="5" t="n">
+        <v>3.1e-05</v>
       </c>
       <c r="H114" t="inlineStr">
         <is>
@@ -9098,25 +9092,27 @@
       </c>
       <c r="B115" t="inlineStr">
         <is>
-          <t>Items not affecting cash</t>
+          <t>Operating activities</t>
         </is>
       </c>
       <c r="C115" t="inlineStr">
         <is>
-          <t>Amortization of capital assets</t>
+          <t>Net loss for the year $ (485,772) $</t>
         </is>
       </c>
       <c r="D115" t="inlineStr"/>
-      <c r="E115" s="5" t="n">
-        <v>0.010505</v>
-      </c>
-      <c r="F115" s="5" t="n">
-        <v>0.00019</v>
-      </c>
-      <c r="G115" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="E115" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F115" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G115" s="5" t="n">
+        <v>-0.901258</v>
       </c>
       <c r="H115" t="inlineStr">
         <is>
@@ -9147,22 +9143,22 @@
       </c>
       <c r="C116" t="inlineStr">
         <is>
-          <t>Loss on disposal of capital assets</t>
+          <t>Settlement of flow-through liability (184,800)</t>
         </is>
       </c>
       <c r="D116" t="inlineStr"/>
-      <c r="E116" s="5" t="n">
-        <v>0.007385</v>
+      <c r="E116" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="F116" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="G116" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="G116" s="5" t="n">
+        <v>-0.07920000000000001</v>
       </c>
       <c r="H116" t="inlineStr">
         <is>
@@ -9193,22 +9189,26 @@
       </c>
       <c r="C117" t="inlineStr">
         <is>
-          <t>Write-down of equipment held for sale</t>
-        </is>
-      </c>
-      <c r="D117" t="inlineStr"/>
+          <t>Share based compensation 32,400</t>
+        </is>
+      </c>
+      <c r="D117" t="inlineStr">
+        <is>
+          <t>StockBasedCompensation</t>
+        </is>
+      </c>
       <c r="E117" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="F117" s="5" t="n">
-        <v>0.009058999999999999</v>
-      </c>
-      <c r="G117" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="F117" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G117" s="5" t="n">
+        <v>0.43475</v>
       </c>
       <c r="H117" t="inlineStr">
         <is>
@@ -9234,29 +9234,27 @@
       </c>
       <c r="B118" t="inlineStr">
         <is>
-          <t>Items not affecting cash</t>
+          <t>Changes in non-cash working capital</t>
         </is>
       </c>
       <c r="C118" t="inlineStr">
         <is>
-          <t>Net changes in non-cash working capital</t>
-        </is>
-      </c>
-      <c r="D118" t="inlineStr">
-        <is>
-          <t>ChangeInWorkingCapital</t>
-        </is>
-      </c>
-      <c r="E118" s="5" t="n">
-        <v>0.161077</v>
-      </c>
-      <c r="F118" s="5" t="n">
-        <v>0.01971</v>
-      </c>
-      <c r="G118" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>Goods and services tax receivable (199,343)</t>
+        </is>
+      </c>
+      <c r="D118" t="inlineStr"/>
+      <c r="E118" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F118" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G118" s="5" t="n">
+        <v>-0.085455</v>
       </c>
       <c r="H118" t="inlineStr">
         <is>
@@ -9282,29 +9280,31 @@
       </c>
       <c r="B119" t="inlineStr">
         <is>
-          <t>Items not affecting cash</t>
+          <t>Changes in non-cash working capital</t>
         </is>
       </c>
       <c r="C119" t="inlineStr">
         <is>
-          <t>Cash used by operating activities</t>
+          <t>Prepaid and deposits 49,747</t>
         </is>
       </c>
       <c r="D119" t="inlineStr">
         <is>
-          <t>OperatingCashFlow</t>
-        </is>
-      </c>
-      <c r="E119" s="5" t="n">
-        <v>-0.243461</v>
-      </c>
-      <c r="F119" s="5" t="n">
-        <v>-0.07709000000000001</v>
-      </c>
-      <c r="G119" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>ChangeInPrepaidAssets</t>
+        </is>
+      </c>
+      <c r="E119" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F119" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G119" s="5" t="n">
+        <v>-0.064042</v>
       </c>
       <c r="H119" t="inlineStr">
         <is>
@@ -9330,25 +9330,31 @@
       </c>
       <c r="B120" t="inlineStr">
         <is>
-          <t>Investing activities</t>
+          <t>Changes in non-cash working capital</t>
         </is>
       </c>
       <c r="C120" t="inlineStr">
         <is>
-          <t>Proceeds from disposal of capital assets and equipment held for sale</t>
-        </is>
-      </c>
-      <c r="D120" t="inlineStr"/>
-      <c r="E120" s="5" t="n">
-        <v>0.00534</v>
-      </c>
-      <c r="F120" s="5" t="n">
-        <v>0.0005999999999999999</v>
-      </c>
-      <c r="G120" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>Accounts payable and accrued liabilities (165,085)</t>
+        </is>
+      </c>
+      <c r="D120" t="inlineStr">
+        <is>
+          <t>ChangeInPayablesAndAccruedExpense</t>
+        </is>
+      </c>
+      <c r="E120" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F120" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G120" s="5" t="n">
+        <v>0.013768</v>
       </c>
       <c r="H120" t="inlineStr">
         <is>
@@ -9374,29 +9380,27 @@
       </c>
       <c r="B121" t="inlineStr">
         <is>
-          <t>Investing activities</t>
+          <t>Changes in non-cash working capital</t>
         </is>
       </c>
       <c r="C121" t="inlineStr">
         <is>
-          <t>Cash from investing activities</t>
-        </is>
-      </c>
-      <c r="D121" t="inlineStr">
-        <is>
-          <t>InvestingCashFlow</t>
-        </is>
-      </c>
-      <c r="E121" s="5" t="n">
-        <v>0.00534</v>
-      </c>
-      <c r="F121" s="5" t="n">
-        <v>0.0005999999999999999</v>
-      </c>
-      <c r="G121" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>Cash used in operating activities (952,853)</t>
+        </is>
+      </c>
+      <c r="D121" t="inlineStr"/>
+      <c r="E121" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F121" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G121" s="5" t="n">
+        <v>-0.681437</v>
       </c>
       <c r="H121" t="inlineStr">
         <is>
@@ -9422,27 +9426,27 @@
       </c>
       <c r="B122" t="inlineStr">
         <is>
-          <t>Financing activities</t>
+          <t>Investing activities</t>
         </is>
       </c>
       <c r="C122" t="inlineStr">
         <is>
-          <t>Payment of cash dividend</t>
+          <t>Exploration and evaluation property acquisition expenditures (note 5) -</t>
         </is>
       </c>
       <c r="D122" t="inlineStr"/>
-      <c r="E122" s="5" t="n">
-        <v>-1.211184</v>
+      <c r="E122" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="F122" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="G122" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="G122" s="5" t="n">
+        <v>-0.377103</v>
       </c>
       <c r="H122" t="inlineStr">
         <is>
@@ -9468,31 +9472,27 @@
       </c>
       <c r="B123" t="inlineStr">
         <is>
-          <t>Financing activities</t>
+          <t>Investing activities</t>
         </is>
       </c>
       <c r="C123" t="inlineStr">
         <is>
-          <t>Cash used by financing activities</t>
-        </is>
-      </c>
-      <c r="D123" t="inlineStr">
-        <is>
-          <t>FinancingCashFlow</t>
-        </is>
-      </c>
-      <c r="E123" s="5" t="n">
-        <v>-1.211184</v>
+          <t>Exploration and evaluation property exploration expenditures, net (note 5) (1,365,763)</t>
+        </is>
+      </c>
+      <c r="D123" t="inlineStr"/>
+      <c r="E123" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="F123" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="G123" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="G123" s="5" t="n">
+        <v>-0.264148</v>
       </c>
       <c r="H123" t="inlineStr">
         <is>
@@ -9518,29 +9518,31 @@
       </c>
       <c r="B124" t="inlineStr">
         <is>
-          <t>Financing activities</t>
+          <t>Investing activities</t>
         </is>
       </c>
       <c r="C124" t="inlineStr">
         <is>
-          <t>Net change in cash during the year</t>
+          <t>Purchase of equipment (note 4) -</t>
         </is>
       </c>
       <c r="D124" t="inlineStr">
         <is>
-          <t>ChangesInCash</t>
-        </is>
-      </c>
-      <c r="E124" s="5" t="n">
-        <v>-1.449305</v>
-      </c>
-      <c r="F124" s="5" t="n">
-        <v>-0.07649</v>
-      </c>
-      <c r="G124" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>PurchaseOfPPE</t>
+        </is>
+      </c>
+      <c r="E124" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F124" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G124" s="5" t="n">
+        <v>-0.06283999999999999</v>
       </c>
       <c r="H124" t="inlineStr">
         <is>
@@ -9566,29 +9568,27 @@
       </c>
       <c r="B125" t="inlineStr">
         <is>
-          <t>Financing activities</t>
+          <t>Investing activities</t>
         </is>
       </c>
       <c r="C125" t="inlineStr">
         <is>
-          <t>Cash and cash equivalents, beginning of the year</t>
-        </is>
-      </c>
-      <c r="D125" t="inlineStr">
-        <is>
-          <t>BeginningCashPosition</t>
-        </is>
-      </c>
-      <c r="E125" s="5" t="n">
-        <v>1.528411</v>
-      </c>
-      <c r="F125" s="5" t="n">
-        <v>0.079106</v>
-      </c>
-      <c r="G125" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>Cash used in investing activities (1,365,763)</t>
+        </is>
+      </c>
+      <c r="D125" t="inlineStr"/>
+      <c r="E125" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F125" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G125" s="5" t="n">
+        <v>-0.704091</v>
       </c>
       <c r="H125" t="inlineStr">
         <is>
@@ -9619,24 +9619,22 @@
       </c>
       <c r="C126" t="inlineStr">
         <is>
-          <t>Cash and cash equivalents, end of the year</t>
-        </is>
-      </c>
-      <c r="D126" t="inlineStr">
-        <is>
-          <t>EndCashPosition</t>
-        </is>
-      </c>
-      <c r="E126" s="5" t="n">
-        <v>0.079106</v>
-      </c>
-      <c r="F126" s="5" t="n">
-        <v>0.002616</v>
-      </c>
-      <c r="G126" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>Proceeds from private placements (note 6) -</t>
+        </is>
+      </c>
+      <c r="D126" t="inlineStr"/>
+      <c r="E126" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F126" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G126" s="5" t="n">
+        <v>5.1905</v>
       </c>
       <c r="H126" t="inlineStr">
         <is>
@@ -9662,31 +9660,27 @@
       </c>
       <c r="B127" t="inlineStr">
         <is>
-          <t>Net changes in non-cash working capital consist of</t>
+          <t>Financing activities</t>
         </is>
       </c>
       <c r="C127" t="inlineStr">
         <is>
-          <t>Accounts receivable</t>
-        </is>
-      </c>
-      <c r="D127" t="inlineStr">
-        <is>
-          <t>ChangeInReceivables</t>
-        </is>
-      </c>
-      <c r="E127" s="5" t="n">
-        <v>0.570016</v>
+          <t>Cash share issuance costs (note 6) (4,433)</t>
+        </is>
+      </c>
+      <c r="D127" t="inlineStr"/>
+      <c r="E127" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="F127" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="G127" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="G127" s="5" t="n">
+        <v>-0.51258</v>
       </c>
       <c r="H127" t="inlineStr">
         <is>
@@ -9712,25 +9706,31 @@
       </c>
       <c r="B128" t="inlineStr">
         <is>
-          <t>Net changes in non-cash working capital consist of</t>
+          <t>Financing activities</t>
         </is>
       </c>
       <c r="C128" t="inlineStr">
         <is>
-          <t>Goods and services tax receivable and other receivable</t>
-        </is>
-      </c>
-      <c r="D128" t="inlineStr"/>
-      <c r="E128" s="5" t="n">
-        <v>-0.009646999999999999</v>
-      </c>
-      <c r="F128" s="5" t="n">
-        <v>0.009289</v>
-      </c>
-      <c r="G128" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>Cash provided by (used in) financing activities (4,433)</t>
+        </is>
+      </c>
+      <c r="D128" t="inlineStr">
+        <is>
+          <t>FinancingCashFlow</t>
+        </is>
+      </c>
+      <c r="E128" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F128" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G128" s="5" t="n">
+        <v>4.67792</v>
       </c>
       <c r="H128" t="inlineStr">
         <is>
@@ -9756,29 +9756,27 @@
       </c>
       <c r="B129" t="inlineStr">
         <is>
-          <t>Net changes in non-cash working capital consist of</t>
+          <t>Financing activities</t>
         </is>
       </c>
       <c r="C129" t="inlineStr">
         <is>
-          <t>Prepaid expenses</t>
-        </is>
-      </c>
-      <c r="D129" t="inlineStr">
-        <is>
-          <t>ChangeInPrepaidAssets</t>
-        </is>
-      </c>
-      <c r="E129" s="5" t="n">
-        <v>0.0273</v>
-      </c>
-      <c r="F129" s="5" t="n">
-        <v>0.002883</v>
-      </c>
-      <c r="G129" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>Net increase (decrease) in cash (2,323,049)</t>
+        </is>
+      </c>
+      <c r="D129" t="inlineStr"/>
+      <c r="E129" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F129" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G129" s="5" t="n">
+        <v>3.292392</v>
       </c>
       <c r="H129" t="inlineStr">
         <is>
@@ -9804,29 +9802,31 @@
       </c>
       <c r="B130" t="inlineStr">
         <is>
-          <t>Net changes in non-cash working capital consist of</t>
+          <t>Financing activities</t>
         </is>
       </c>
       <c r="C130" t="inlineStr">
         <is>
-          <t>Accounts payable and accrued liabilities</t>
+          <t>Cash, beginning of the year 3,292,639</t>
         </is>
       </c>
       <c r="D130" t="inlineStr">
         <is>
-          <t>ChangeInPayablesAndAccruedExpense</t>
-        </is>
-      </c>
-      <c r="E130" s="5" t="n">
-        <v>-0.426592</v>
-      </c>
-      <c r="F130" s="5" t="n">
-        <v>0.007538</v>
-      </c>
-      <c r="G130" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>BeginningCashPosition</t>
+        </is>
+      </c>
+      <c r="E130" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F130" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G130" s="5" t="n">
+        <v>0.000247</v>
       </c>
       <c r="H130" t="inlineStr">
         <is>
@@ -9852,25 +9852,31 @@
       </c>
       <c r="B131" t="inlineStr">
         <is>
-          <t>Net changes in non-cash working capital consist of</t>
+          <t>Financing activities</t>
         </is>
       </c>
       <c r="C131" t="inlineStr">
         <is>
-          <t>Net changes in non-cash working capital consist of total</t>
-        </is>
-      </c>
-      <c r="D131" t="inlineStr"/>
-      <c r="E131" s="5" t="n">
-        <v>0.161077</v>
-      </c>
-      <c r="F131" s="5" t="n">
-        <v>0.01971</v>
-      </c>
-      <c r="G131" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>Cash, end of the year $ 969,590 $</t>
+        </is>
+      </c>
+      <c r="D131" t="inlineStr">
+        <is>
+          <t>EndCashPosition</t>
+        </is>
+      </c>
+      <c r="E131" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F131" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G131" s="5" t="n">
+        <v>3.292639</v>
       </c>
       <c r="H131" t="inlineStr">
         <is>
@@ -9896,26 +9902,24 @@
       </c>
       <c r="B132" t="inlineStr">
         <is>
-          <t>Other information on cash flows</t>
+          <t>Operating activities</t>
         </is>
       </c>
       <c r="C132" t="inlineStr">
         <is>
-          <t>Income taxes paid</t>
+          <t>Net loss for the year</t>
         </is>
       </c>
       <c r="D132" t="inlineStr">
         <is>
-          <t>IncomeTaxPaidSupplementalData</t>
+          <t>NetIncomeFromContinuingOperations</t>
         </is>
       </c>
       <c r="E132" s="5" t="n">
-        <v>0.000175</v>
-      </c>
-      <c r="F132" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>-0.422428</v>
+      </c>
+      <c r="F132" s="5" t="n">
+        <v>-0.106049</v>
       </c>
       <c r="G132" t="inlineStr">
         <is>
@@ -9946,28 +9950,20 @@
       </c>
       <c r="B133" t="inlineStr">
         <is>
-          <t>Other information on cash flows</t>
+          <t>Items not affecting cash</t>
         </is>
       </c>
       <c r="C133" t="inlineStr">
         <is>
-          <t>Interest paid</t>
-        </is>
-      </c>
-      <c r="D133" t="inlineStr">
-        <is>
-          <t>InterestPaidSupplementalData</t>
-        </is>
-      </c>
-      <c r="E133" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F133" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>Amortization of capital assets</t>
+        </is>
+      </c>
+      <c r="D133" t="inlineStr"/>
+      <c r="E133" s="5" t="n">
+        <v>0.010505</v>
+      </c>
+      <c r="F133" s="5" t="n">
+        <v>0.00019</v>
       </c>
       <c r="G133" t="inlineStr">
         <is>
@@ -9993,20 +9989,22 @@
     <row r="134">
       <c r="A134" t="inlineStr">
         <is>
-          <t>income_statement</t>
-        </is>
-      </c>
-      <c r="B134" t="inlineStr"/>
+          <t>cash_flow</t>
+        </is>
+      </c>
+      <c r="B134" t="inlineStr">
+        <is>
+          <t>Items not affecting cash</t>
+        </is>
+      </c>
       <c r="C134" t="inlineStr">
         <is>
-          <t>August 31, 2025 August</t>
+          <t>Loss on disposal of capital assets</t>
         </is>
       </c>
       <c r="D134" t="inlineStr"/>
-      <c r="E134" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="E134" s="5" t="n">
+        <v>0.007385</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
@@ -10023,43 +10021,41 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I134" s="5" t="n">
-        <v>0.002024</v>
-      </c>
-      <c r="J134" s="5" t="n">
-        <v>3.1e-05</v>
+      <c r="I134" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J134" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
     </row>
     <row r="135">
       <c r="A135" t="inlineStr">
         <is>
-          <t>income_statement</t>
+          <t>cash_flow</t>
         </is>
       </c>
       <c r="B135" t="inlineStr">
         <is>
-          <t>Expenses</t>
+          <t>Items not affecting cash</t>
         </is>
       </c>
       <c r="C135" t="inlineStr">
         <is>
-          <t>Marketing $</t>
-        </is>
-      </c>
-      <c r="D135" t="inlineStr">
-        <is>
-          <t>OtherOperatingExpenses</t>
-        </is>
-      </c>
+          <t>Write-down of equipment held for sale</t>
+        </is>
+      </c>
+      <c r="D135" t="inlineStr"/>
       <c r="E135" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="F135" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="F135" s="5" t="n">
+        <v>0.009058999999999999</v>
       </c>
       <c r="G135" t="inlineStr">
         <is>
@@ -10071,87 +10067,91 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I135" s="5" t="n">
-        <v>0.86105</v>
-      </c>
-      <c r="J135" s="5" t="n">
-        <v>1.006573</v>
+      <c r="I135" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J135" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
     </row>
     <row r="136">
       <c r="A136" t="inlineStr">
         <is>
-          <t>income_statement</t>
+          <t>cash_flow</t>
         </is>
       </c>
       <c r="B136" t="inlineStr">
         <is>
-          <t>Expenses</t>
+          <t>Items not affecting cash</t>
         </is>
       </c>
       <c r="C136" t="inlineStr">
         <is>
-          <t>General and administration</t>
+          <t>Net changes in non-cash working capital</t>
         </is>
       </c>
       <c r="D136" t="inlineStr">
         <is>
-          <t>GeneralAndAdministrativeExpense</t>
-        </is>
-      </c>
-      <c r="E136" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F136" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G136" s="5" t="n">
-        <v>0.08511000000000001</v>
-      </c>
-      <c r="H136" s="5" t="n">
-        <v>0.247233</v>
-      </c>
-      <c r="I136" s="5" t="n">
-        <v>0.430683</v>
-      </c>
-      <c r="J136" s="5" t="n">
-        <v>1.314441</v>
+          <t>ChangeInWorkingCapital</t>
+        </is>
+      </c>
+      <c r="E136" s="5" t="n">
+        <v>0.161077</v>
+      </c>
+      <c r="F136" s="5" t="n">
+        <v>0.01971</v>
+      </c>
+      <c r="G136" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H136" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I136" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J136" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
     </row>
     <row r="137">
       <c r="A137" t="inlineStr">
         <is>
-          <t>income_statement</t>
+          <t>cash_flow</t>
         </is>
       </c>
       <c r="B137" t="inlineStr">
         <is>
-          <t>Expenses</t>
+          <t>Items not affecting cash</t>
         </is>
       </c>
       <c r="C137" t="inlineStr">
         <is>
-          <t>Management fees (note 9)</t>
+          <t>Cash used by operating activities</t>
         </is>
       </c>
       <c r="D137" t="inlineStr">
         <is>
-          <t>SellingGeneralAndAdministration</t>
-        </is>
-      </c>
-      <c r="E137" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F137" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>OperatingCashFlow</t>
+        </is>
+      </c>
+      <c r="E137" s="5" t="n">
+        <v>-0.243461</v>
+      </c>
+      <c r="F137" s="5" t="n">
+        <v>-0.07709000000000001</v>
       </c>
       <c r="G137" t="inlineStr">
         <is>
@@ -10163,158 +10163,178 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I137" s="5" t="n">
-        <v>0.686685</v>
-      </c>
-      <c r="J137" s="5" t="n">
-        <v>1.153451</v>
+      <c r="I137" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J137" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
     </row>
     <row r="138">
       <c r="A138" t="inlineStr">
         <is>
-          <t>income_statement</t>
+          <t>cash_flow</t>
         </is>
       </c>
       <c r="B138" t="inlineStr">
         <is>
-          <t>Expenses</t>
+          <t>Investing activities</t>
         </is>
       </c>
       <c r="C138" t="inlineStr">
         <is>
-          <t>Professional fees</t>
-        </is>
-      </c>
-      <c r="D138" t="inlineStr">
-        <is>
-          <t>ProfessionalExpenseAndContractServicesExpense</t>
-        </is>
-      </c>
+          <t>Proceeds from disposal of capital assets and equipment held for sale</t>
+        </is>
+      </c>
+      <c r="D138" t="inlineStr"/>
       <c r="E138" s="5" t="n">
-        <v>0.147249</v>
+        <v>0.00534</v>
       </c>
       <c r="F138" s="5" t="n">
-        <v>0.052041</v>
-      </c>
-      <c r="G138" s="5" t="n">
-        <v>0.100633</v>
-      </c>
-      <c r="H138" s="5" t="n">
-        <v>0.101979</v>
-      </c>
-      <c r="I138" s="5" t="n">
-        <v>0.469212</v>
-      </c>
-      <c r="J138" s="5" t="n">
-        <v>1.657254</v>
+        <v>0.0005999999999999999</v>
+      </c>
+      <c r="G138" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H138" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I138" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J138" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
     </row>
     <row r="139">
       <c r="A139" t="inlineStr">
         <is>
-          <t>income_statement</t>
+          <t>cash_flow</t>
         </is>
       </c>
       <c r="B139" t="inlineStr">
         <is>
-          <t>Expenses</t>
+          <t>Investing activities</t>
         </is>
       </c>
       <c r="C139" t="inlineStr">
         <is>
-          <t>Regulatory and filing fees</t>
-        </is>
-      </c>
-      <c r="D139" t="inlineStr"/>
-      <c r="E139" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F139" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G139" s="5" t="n">
-        <v>0.022953</v>
-      </c>
-      <c r="H139" s="5" t="n">
-        <v>0.044755</v>
-      </c>
-      <c r="I139" s="5" t="n">
-        <v>0.148469</v>
-      </c>
-      <c r="J139" s="5" t="n">
-        <v>0.107636</v>
+          <t>Cash from investing activities</t>
+        </is>
+      </c>
+      <c r="D139" t="inlineStr">
+        <is>
+          <t>InvestingCashFlow</t>
+        </is>
+      </c>
+      <c r="E139" s="5" t="n">
+        <v>0.00534</v>
+      </c>
+      <c r="F139" s="5" t="n">
+        <v>0.0005999999999999999</v>
+      </c>
+      <c r="G139" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H139" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I139" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J139" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
     </row>
     <row r="140">
       <c r="A140" t="inlineStr">
         <is>
-          <t>income_statement</t>
+          <t>cash_flow</t>
         </is>
       </c>
       <c r="B140" t="inlineStr">
         <is>
-          <t>Expenses</t>
+          <t>Financing activities</t>
         </is>
       </c>
       <c r="C140" t="inlineStr">
         <is>
-          <t>Expenses total</t>
-        </is>
-      </c>
-      <c r="D140" t="inlineStr">
-        <is>
-          <t>OperatingExpense</t>
-        </is>
-      </c>
+          <t>Payment of cash dividend</t>
+        </is>
+      </c>
+      <c r="D140" t="inlineStr"/>
       <c r="E140" s="5" t="n">
-        <v>1.019984</v>
-      </c>
-      <c r="F140" s="5" t="n">
-        <v>0.09705999999999999</v>
-      </c>
-      <c r="G140" s="5" t="n">
-        <v>0.655075</v>
-      </c>
-      <c r="H140" s="5" t="n">
-        <v>1.031904</v>
-      </c>
-      <c r="I140" s="5" t="n">
-        <v>2.596099</v>
-      </c>
-      <c r="J140" s="5" t="n">
-        <v>5.239355</v>
+        <v>-1.211184</v>
+      </c>
+      <c r="F140" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G140" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H140" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I140" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J140" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
     </row>
     <row r="141">
       <c r="A141" t="inlineStr">
         <is>
-          <t>income_statement</t>
+          <t>cash_flow</t>
         </is>
       </c>
       <c r="B141" t="inlineStr">
         <is>
-          <t>Other income (expenses)</t>
+          <t>Financing activities</t>
         </is>
       </c>
       <c r="C141" t="inlineStr">
         <is>
-          <t>Interest income</t>
+          <t>Cash used by financing activities</t>
         </is>
       </c>
       <c r="D141" t="inlineStr">
         <is>
-          <t>InterestIncomeNonOperating</t>
-        </is>
-      </c>
-      <c r="E141" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>FinancingCashFlow</t>
+        </is>
+      </c>
+      <c r="E141" s="5" t="n">
+        <v>-1.211184</v>
       </c>
       <c r="F141" t="inlineStr">
         <is>
@@ -10331,43 +10351,43 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I141" s="5" t="n">
-        <v>0.228167</v>
-      </c>
-      <c r="J141" s="5" t="n">
-        <v>0.713803</v>
+      <c r="I141" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J141" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
     </row>
     <row r="142">
       <c r="A142" t="inlineStr">
         <is>
-          <t>income_statement</t>
+          <t>cash_flow</t>
         </is>
       </c>
       <c r="B142" t="inlineStr">
         <is>
-          <t>Other income (expenses)</t>
+          <t>Financing activities</t>
         </is>
       </c>
       <c r="C142" t="inlineStr">
         <is>
-          <t>Foreign exchange gain (loss)</t>
+          <t>Net change in cash during the year</t>
         </is>
       </c>
       <c r="D142" t="inlineStr">
         <is>
-          <t>OtherIncomeExpense</t>
-        </is>
-      </c>
-      <c r="E142" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F142" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>ChangesInCash</t>
+        </is>
+      </c>
+      <c r="E142" s="5" t="n">
+        <v>-1.449305</v>
+      </c>
+      <c r="F142" s="5" t="n">
+        <v>-0.07649</v>
       </c>
       <c r="G142" t="inlineStr">
         <is>
@@ -10379,39 +10399,43 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I142" s="5" t="n">
-        <v>-0.005925</v>
-      </c>
-      <c r="J142" s="5" t="n">
-        <v>-0.207256</v>
+      <c r="I142" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J142" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
     </row>
     <row r="143">
       <c r="A143" t="inlineStr">
         <is>
-          <t>income_statement</t>
+          <t>cash_flow</t>
         </is>
       </c>
       <c r="B143" t="inlineStr">
         <is>
-          <t>Other income (expenses)</t>
+          <t>Financing activities</t>
         </is>
       </c>
       <c r="C143" t="inlineStr">
         <is>
-          <t>Share-based compensation (note 7)</t>
-        </is>
-      </c>
-      <c r="D143" t="inlineStr"/>
-      <c r="E143" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F143" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>Cash and cash equivalents, beginning of the year</t>
+        </is>
+      </c>
+      <c r="D143" t="inlineStr">
+        <is>
+          <t>BeginningCashPosition</t>
+        </is>
+      </c>
+      <c r="E143" s="5" t="n">
+        <v>1.528411</v>
+      </c>
+      <c r="F143" s="5" t="n">
+        <v>0.079106</v>
       </c>
       <c r="G143" t="inlineStr">
         <is>
@@ -10423,43 +10447,43 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I143" s="5" t="n">
-        <v>-5.3646</v>
-      </c>
-      <c r="J143" s="5" t="n">
-        <v>-5.85232</v>
+      <c r="I143" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J143" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
     </row>
     <row r="144">
       <c r="A144" t="inlineStr">
         <is>
-          <t>income_statement</t>
+          <t>cash_flow</t>
         </is>
       </c>
       <c r="B144" t="inlineStr">
         <is>
-          <t>Other income (expenses)</t>
+          <t>Financing activities</t>
         </is>
       </c>
       <c r="C144" t="inlineStr">
         <is>
-          <t>Net loss for the year</t>
+          <t>Cash and cash equivalents, end of the year</t>
         </is>
       </c>
       <c r="D144" t="inlineStr">
         <is>
-          <t>NetIncome</t>
-        </is>
-      </c>
-      <c r="E144" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F144" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>EndCashPosition</t>
+        </is>
+      </c>
+      <c r="E144" s="5" t="n">
+        <v>0.079106</v>
+      </c>
+      <c r="F144" s="5" t="n">
+        <v>0.002616</v>
       </c>
       <c r="G144" t="inlineStr">
         <is>
@@ -10471,38 +10495,40 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I144" s="5" t="n">
-        <v>-7.738457</v>
-      </c>
-      <c r="J144" s="5" t="n">
-        <v>-10.585128</v>
+      <c r="I144" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J144" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
     </row>
     <row r="145">
       <c r="A145" t="inlineStr">
         <is>
-          <t>income_statement</t>
+          <t>cash_flow</t>
         </is>
       </c>
       <c r="B145" t="inlineStr">
         <is>
-          <t>Other income (expenses)</t>
+          <t>Net changes in non-cash working capital consist of</t>
         </is>
       </c>
       <c r="C145" t="inlineStr">
         <is>
-          <t>Basic and diluted loss per common share</t>
+          <t>Accounts receivable</t>
         </is>
       </c>
       <c r="D145" t="inlineStr">
         <is>
-          <t>BasicEPS</t>
-        </is>
-      </c>
-      <c r="E145" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>ChangeInReceivables</t>
+        </is>
+      </c>
+      <c r="E145" s="5" t="n">
+        <v>0.570016</v>
       </c>
       <c r="F145" t="inlineStr">
         <is>
@@ -10519,39 +10545,39 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I145" s="5" t="n">
-        <v>-1.3e-07</v>
-      </c>
-      <c r="J145" s="5" t="n">
-        <v>-1.1e-07</v>
+      <c r="I145" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J145" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
     </row>
     <row r="146">
       <c r="A146" t="inlineStr">
         <is>
-          <t>income_statement</t>
+          <t>cash_flow</t>
         </is>
       </c>
       <c r="B146" t="inlineStr">
         <is>
-          <t>Other income (expenses)</t>
+          <t>Net changes in non-cash working capital consist of</t>
         </is>
       </c>
       <c r="C146" t="inlineStr">
         <is>
-          <t>Basic and diluted weighted average number</t>
+          <t>Goods and services tax receivable and other receivable</t>
         </is>
       </c>
       <c r="D146" t="inlineStr"/>
-      <c r="E146" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F146" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="E146" s="5" t="n">
+        <v>-0.009646999999999999</v>
+      </c>
+      <c r="F146" s="5" t="n">
+        <v>0.009289</v>
       </c>
       <c r="G146" t="inlineStr">
         <is>
@@ -10563,39 +10589,43 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I146" s="5" t="n">
-        <v>60.245282</v>
-      </c>
-      <c r="J146" s="5" t="n">
-        <v>93.10255100000001</v>
+      <c r="I146" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J146" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
     </row>
     <row r="147">
       <c r="A147" t="inlineStr">
         <is>
-          <t>income_statement</t>
+          <t>cash_flow</t>
         </is>
       </c>
       <c r="B147" t="inlineStr">
         <is>
-          <t>Other comprehensive income (loss)</t>
+          <t>Net changes in non-cash working capital consist of</t>
         </is>
       </c>
       <c r="C147" t="inlineStr">
         <is>
-          <t>Foreign currency translation adjustment</t>
-        </is>
-      </c>
-      <c r="D147" t="inlineStr"/>
-      <c r="E147" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F147" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>Prepaid expenses</t>
+        </is>
+      </c>
+      <c r="D147" t="inlineStr">
+        <is>
+          <t>ChangeInPrepaidAssets</t>
+        </is>
+      </c>
+      <c r="E147" s="5" t="n">
+        <v>0.0273</v>
+      </c>
+      <c r="F147" s="5" t="n">
+        <v>0.002883</v>
       </c>
       <c r="G147" t="inlineStr">
         <is>
@@ -10612,40 +10642,38 @@
           <t>-</t>
         </is>
       </c>
-      <c r="J147" s="5" t="n">
-        <v>-0.018059</v>
+      <c r="J147" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
     </row>
     <row r="148">
       <c r="A148" t="inlineStr">
         <is>
-          <t>income_statement</t>
+          <t>cash_flow</t>
         </is>
       </c>
       <c r="B148" t="inlineStr">
         <is>
-          <t>Other comprehensive income (loss)</t>
+          <t>Net changes in non-cash working capital consist of</t>
         </is>
       </c>
       <c r="C148" t="inlineStr">
         <is>
-          <t>Net and comprehensive loss for the year $</t>
+          <t>Accounts payable and accrued liabilities</t>
         </is>
       </c>
       <c r="D148" t="inlineStr">
         <is>
-          <t>NetIncome</t>
-        </is>
-      </c>
-      <c r="E148" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F148" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>ChangeInPayablesAndAccruedExpense</t>
+        </is>
+      </c>
+      <c r="E148" s="5" t="n">
+        <v>-0.426592</v>
+      </c>
+      <c r="F148" s="5" t="n">
+        <v>0.007538</v>
       </c>
       <c r="G148" t="inlineStr">
         <is>
@@ -10657,54 +10685,54 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I148" s="5" t="n">
-        <v>-7.738457</v>
-      </c>
-      <c r="J148" s="5" t="n">
-        <v>-10.603187</v>
+      <c r="I148" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J148" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
     </row>
     <row r="149">
       <c r="A149" t="inlineStr">
         <is>
-          <t>income_statement</t>
+          <t>cash_flow</t>
         </is>
       </c>
       <c r="B149" t="inlineStr">
         <is>
-          <t>Expenses</t>
+          <t>Net changes in non-cash working capital consist of</t>
         </is>
       </c>
       <c r="C149" t="inlineStr">
         <is>
-          <t>Marketing (Note 8) $</t>
-        </is>
-      </c>
-      <c r="D149" t="inlineStr">
-        <is>
-          <t>OtherOperatingExpenses</t>
-        </is>
-      </c>
-      <c r="E149" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F149" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>Net changes in non-cash working capital consist of total</t>
+        </is>
+      </c>
+      <c r="D149" t="inlineStr"/>
+      <c r="E149" s="5" t="n">
+        <v>0.161077</v>
+      </c>
+      <c r="F149" s="5" t="n">
+        <v>0.01971</v>
       </c>
       <c r="G149" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="H149" s="5" t="n">
-        <v>0.458437</v>
-      </c>
-      <c r="I149" s="5" t="n">
-        <v>0.86105</v>
+      <c r="H149" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I149" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="J149" t="inlineStr">
         <is>
@@ -10715,28 +10743,26 @@
     <row r="150">
       <c r="A150" t="inlineStr">
         <is>
-          <t>income_statement</t>
+          <t>cash_flow</t>
         </is>
       </c>
       <c r="B150" t="inlineStr">
         <is>
-          <t>Expenses</t>
+          <t>Other information on cash flows</t>
         </is>
       </c>
       <c r="C150" t="inlineStr">
         <is>
-          <t>Management fees (Note 8)</t>
+          <t>Income taxes paid</t>
         </is>
       </c>
       <c r="D150" t="inlineStr">
         <is>
-          <t>SellingGeneralAndAdministration</t>
-        </is>
-      </c>
-      <c r="E150" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>IncomeTaxPaidSupplementalData</t>
+        </is>
+      </c>
+      <c r="E150" s="5" t="n">
+        <v>0.000175</v>
       </c>
       <c r="F150" t="inlineStr">
         <is>
@@ -10748,11 +10774,15 @@
           <t>-</t>
         </is>
       </c>
-      <c r="H150" s="5" t="n">
-        <v>0.1795</v>
-      </c>
-      <c r="I150" s="5" t="n">
-        <v>0.686685</v>
+      <c r="H150" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I150" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="J150" t="inlineStr">
         <is>
@@ -10763,22 +10793,22 @@
     <row r="151">
       <c r="A151" t="inlineStr">
         <is>
-          <t>income_statement</t>
+          <t>cash_flow</t>
         </is>
       </c>
       <c r="B151" t="inlineStr">
         <is>
-          <t>Expenses</t>
+          <t>Other information on cash flows</t>
         </is>
       </c>
       <c r="C151" t="inlineStr">
         <is>
-          <t>Total expense</t>
+          <t>Interest paid</t>
         </is>
       </c>
       <c r="D151" t="inlineStr">
         <is>
-          <t>OperatingExpense</t>
+          <t>InterestPaidSupplementalData</t>
         </is>
       </c>
       <c r="E151" t="inlineStr">
@@ -10796,11 +10826,15 @@
           <t>-</t>
         </is>
       </c>
-      <c r="H151" s="5" t="n">
-        <v>1.031904</v>
-      </c>
-      <c r="I151" s="5" t="n">
-        <v>2.596099</v>
+      <c r="H151" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I151" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="J151" t="inlineStr">
         <is>
@@ -10814,21 +10848,13 @@
           <t>income_statement</t>
         </is>
       </c>
-      <c r="B152" t="inlineStr">
-        <is>
-          <t>Other income</t>
-        </is>
-      </c>
+      <c r="B152" t="inlineStr"/>
       <c r="C152" t="inlineStr">
         <is>
-          <t>Interest income</t>
-        </is>
-      </c>
-      <c r="D152" t="inlineStr">
-        <is>
-          <t>InterestIncomeNonOperating</t>
-        </is>
-      </c>
+          <t>August 31, 2025 August</t>
+        </is>
+      </c>
+      <c r="D152" t="inlineStr"/>
       <c r="E152" t="inlineStr">
         <is>
           <t>-</t>
@@ -10839,19 +10865,21 @@
           <t>-</t>
         </is>
       </c>
-      <c r="G152" s="5" t="n">
-        <v>0.016903</v>
-      </c>
-      <c r="H152" s="5" t="n">
-        <v>0.04075</v>
+      <c r="G152" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H152" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="I152" s="5" t="n">
-        <v>0.228167</v>
-      </c>
-      <c r="J152" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>0.002024</v>
+      </c>
+      <c r="J152" s="5" t="n">
+        <v>3.1e-05</v>
       </c>
     </row>
     <row r="153">
@@ -10862,15 +10890,19 @@
       </c>
       <c r="B153" t="inlineStr">
         <is>
-          <t>Other income</t>
+          <t>Expenses</t>
         </is>
       </c>
       <c r="C153" t="inlineStr">
         <is>
-          <t>Foreign currency exchange gain (loss)</t>
-        </is>
-      </c>
-      <c r="D153" t="inlineStr"/>
+          <t>Marketing $</t>
+        </is>
+      </c>
+      <c r="D153" t="inlineStr">
+        <is>
+          <t>OtherOperatingExpenses</t>
+        </is>
+      </c>
       <c r="E153" t="inlineStr">
         <is>
           <t>-</t>
@@ -10892,12 +10924,10 @@
         </is>
       </c>
       <c r="I153" s="5" t="n">
-        <v>-0.005925</v>
-      </c>
-      <c r="J153" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>0.86105</v>
+      </c>
+      <c r="J153" s="5" t="n">
+        <v>1.006573</v>
       </c>
     </row>
     <row r="154">
@@ -10908,15 +10938,19 @@
       </c>
       <c r="B154" t="inlineStr">
         <is>
-          <t>Other income</t>
+          <t>Expenses</t>
         </is>
       </c>
       <c r="C154" t="inlineStr">
         <is>
-          <t>Share based compensation</t>
-        </is>
-      </c>
-      <c r="D154" t="inlineStr"/>
+          <t>General and administration</t>
+        </is>
+      </c>
+      <c r="D154" t="inlineStr">
+        <is>
+          <t>GeneralAndAdministrativeExpense</t>
+        </is>
+      </c>
       <c r="E154" t="inlineStr">
         <is>
           <t>-</t>
@@ -10928,18 +10962,16 @@
         </is>
       </c>
       <c r="G154" s="5" t="n">
-        <v>-0.0324</v>
+        <v>0.08511000000000001</v>
       </c>
       <c r="H154" s="5" t="n">
-        <v>-0.8711</v>
+        <v>0.247233</v>
       </c>
       <c r="I154" s="5" t="n">
-        <v>-5.3646</v>
-      </c>
-      <c r="J154" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>0.430683</v>
+      </c>
+      <c r="J154" s="5" t="n">
+        <v>1.314441</v>
       </c>
     </row>
     <row r="155">
@@ -10950,17 +10982,17 @@
       </c>
       <c r="B155" t="inlineStr">
         <is>
-          <t>Other income</t>
+          <t>Expenses</t>
         </is>
       </c>
       <c r="C155" t="inlineStr">
         <is>
-          <t>Net and comprehensive loss for the year $</t>
+          <t>Management fees (note 9)</t>
         </is>
       </c>
       <c r="D155" t="inlineStr">
         <is>
-          <t>NetIncome</t>
+          <t>SellingGeneralAndAdministration</t>
         </is>
       </c>
       <c r="E155" t="inlineStr">
@@ -10973,19 +11005,21 @@
           <t>-</t>
         </is>
       </c>
-      <c r="G155" s="5" t="n">
-        <v>-0.485772</v>
-      </c>
-      <c r="H155" s="5" t="n">
-        <v>-1.862254</v>
+      <c r="G155" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H155" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="I155" s="5" t="n">
-        <v>-7.738457</v>
-      </c>
-      <c r="J155" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>0.686685</v>
+      </c>
+      <c r="J155" s="5" t="n">
+        <v>1.153451</v>
       </c>
     </row>
     <row r="156">
@@ -10996,42 +11030,36 @@
       </c>
       <c r="B156" t="inlineStr">
         <is>
-          <t>Other income</t>
+          <t>Expenses</t>
         </is>
       </c>
       <c r="C156" t="inlineStr">
         <is>
-          <t>Basic and diluted loss per common share $</t>
+          <t>Professional fees</t>
         </is>
       </c>
       <c r="D156" t="inlineStr">
         <is>
-          <t>BasicEPS</t>
-        </is>
-      </c>
-      <c r="E156" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F156" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>ProfessionalExpenseAndContractServicesExpense</t>
+        </is>
+      </c>
+      <c r="E156" s="5" t="n">
+        <v>0.147249</v>
+      </c>
+      <c r="F156" s="5" t="n">
+        <v>0.052041</v>
       </c>
       <c r="G156" s="5" t="n">
-        <v>-2e-08</v>
+        <v>0.100633</v>
       </c>
       <c r="H156" s="5" t="n">
-        <v>-5.999999999999999e-08</v>
+        <v>0.101979</v>
       </c>
       <c r="I156" s="5" t="n">
-        <v>-1.3e-07</v>
-      </c>
-      <c r="J156" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>0.469212</v>
+      </c>
+      <c r="J156" s="5" t="n">
+        <v>1.657254</v>
       </c>
     </row>
     <row r="157">
@@ -11042,19 +11070,15 @@
       </c>
       <c r="B157" t="inlineStr">
         <is>
-          <t>Basic and diluted weighted average</t>
+          <t>Expenses</t>
         </is>
       </c>
       <c r="C157" t="inlineStr">
         <is>
-          <t>Basic and diluted weighted average number of common shares outstanding</t>
-        </is>
-      </c>
-      <c r="D157" t="inlineStr">
-        <is>
-          <t>SharesOutstanding</t>
-        </is>
-      </c>
+          <t>Regulatory and filing fees</t>
+        </is>
+      </c>
+      <c r="D157" t="inlineStr"/>
       <c r="E157" t="inlineStr">
         <is>
           <t>-</t>
@@ -11066,18 +11090,16 @@
         </is>
       </c>
       <c r="G157" s="5" t="n">
-        <v>26.217</v>
+        <v>0.022953</v>
       </c>
       <c r="H157" s="5" t="n">
-        <v>33.852304</v>
+        <v>0.044755</v>
       </c>
       <c r="I157" s="5" t="n">
-        <v>60.245282</v>
-      </c>
-      <c r="J157" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>0.148469</v>
+      </c>
+      <c r="J157" s="5" t="n">
+        <v>0.107636</v>
       </c>
     </row>
     <row r="158">
@@ -11093,39 +11115,31 @@
       </c>
       <c r="C158" t="inlineStr">
         <is>
-          <t>Advertising and promotion $</t>
+          <t>Expenses total</t>
         </is>
       </c>
       <c r="D158" t="inlineStr">
         <is>
-          <t>OtherOperatingExpenses</t>
-        </is>
-      </c>
-      <c r="E158" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F158" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>OperatingExpense</t>
+        </is>
+      </c>
+      <c r="E158" s="5" t="n">
+        <v>1.019984</v>
+      </c>
+      <c r="F158" s="5" t="n">
+        <v>0.09705999999999999</v>
       </c>
       <c r="G158" s="5" t="n">
-        <v>0.208018</v>
+        <v>0.655075</v>
       </c>
       <c r="H158" s="5" t="n">
-        <v>0.458437</v>
-      </c>
-      <c r="I158" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J158" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>1.031904</v>
+      </c>
+      <c r="I158" s="5" t="n">
+        <v>2.596099</v>
+      </c>
+      <c r="J158" s="5" t="n">
+        <v>5.239355</v>
       </c>
     </row>
     <row r="159">
@@ -11136,17 +11150,17 @@
       </c>
       <c r="B159" t="inlineStr">
         <is>
-          <t>Expenses</t>
+          <t>Other income (expenses)</t>
         </is>
       </c>
       <c r="C159" t="inlineStr">
         <is>
-          <t>Management fees</t>
+          <t>Interest income</t>
         </is>
       </c>
       <c r="D159" t="inlineStr">
         <is>
-          <t>SellingGeneralAndAdministration</t>
+          <t>InterestIncomeNonOperating</t>
         </is>
       </c>
       <c r="E159" t="inlineStr">
@@ -11159,21 +11173,21 @@
           <t>-</t>
         </is>
       </c>
-      <c r="G159" s="5" t="n">
-        <v>0.204</v>
-      </c>
-      <c r="H159" s="5" t="n">
-        <v>0.1795</v>
-      </c>
-      <c r="I159" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J159" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="G159" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H159" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I159" s="5" t="n">
+        <v>0.228167</v>
+      </c>
+      <c r="J159" s="5" t="n">
+        <v>0.713803</v>
       </c>
     </row>
     <row r="160">
@@ -11184,15 +11198,19 @@
       </c>
       <c r="B160" t="inlineStr">
         <is>
-          <t>Expenses</t>
+          <t>Other income (expenses)</t>
         </is>
       </c>
       <c r="C160" t="inlineStr">
         <is>
-          <t>Project evaluation</t>
-        </is>
-      </c>
-      <c r="D160" t="inlineStr"/>
+          <t>Foreign exchange gain (loss)</t>
+        </is>
+      </c>
+      <c r="D160" t="inlineStr">
+        <is>
+          <t>OtherIncomeExpense</t>
+        </is>
+      </c>
       <c r="E160" t="inlineStr">
         <is>
           <t>-</t>
@@ -11203,23 +11221,21 @@
           <t>-</t>
         </is>
       </c>
-      <c r="G160" s="5" t="n">
-        <v>0.034361</v>
+      <c r="G160" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="H160" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="I160" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J160" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="I160" s="5" t="n">
+        <v>-0.005925</v>
+      </c>
+      <c r="J160" s="5" t="n">
+        <v>-0.207256</v>
       </c>
     </row>
     <row r="161">
@@ -11230,12 +11246,12 @@
       </c>
       <c r="B161" t="inlineStr">
         <is>
-          <t>Other income</t>
+          <t>Other income (expenses)</t>
         </is>
       </c>
       <c r="C161" t="inlineStr">
         <is>
-          <t>Settlement of flow-through liability</t>
+          <t>Share-based compensation (note 7)</t>
         </is>
       </c>
       <c r="D161" t="inlineStr"/>
@@ -11249,23 +11265,21 @@
           <t>-</t>
         </is>
       </c>
-      <c r="G161" s="5" t="n">
-        <v>0.1848</v>
+      <c r="G161" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="H161" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="I161" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J161" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="I161" s="5" t="n">
+        <v>-5.3646</v>
+      </c>
+      <c r="J161" s="5" t="n">
+        <v>-5.85232</v>
       </c>
     </row>
     <row r="162">
@@ -11274,22 +11288,30 @@
           <t>income_statement</t>
         </is>
       </c>
-      <c r="B162" t="inlineStr"/>
+      <c r="B162" t="inlineStr">
+        <is>
+          <t>Other income (expenses)</t>
+        </is>
+      </c>
       <c r="C162" t="inlineStr">
         <is>
-          <t>Revenue</t>
+          <t>Net loss for the year</t>
         </is>
       </c>
       <c r="D162" t="inlineStr">
         <is>
-          <t>TotalRevenue</t>
-        </is>
-      </c>
-      <c r="E162" s="5" t="n">
-        <v>0.633741</v>
-      </c>
-      <c r="F162" s="5" t="n">
-        <v>6.999999999999999e-05</v>
+          <t>NetIncome</t>
+        </is>
+      </c>
+      <c r="E162" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F162" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="G162" t="inlineStr">
         <is>
@@ -11301,15 +11323,11 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I162" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J162" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="I162" s="5" t="n">
+        <v>-7.738457</v>
+      </c>
+      <c r="J162" s="5" t="n">
+        <v>-10.585128</v>
       </c>
     </row>
     <row r="163">
@@ -11320,21 +11338,23 @@
       </c>
       <c r="B163" t="inlineStr">
         <is>
-          <t>Expenses</t>
+          <t>Other income (expenses)</t>
         </is>
       </c>
       <c r="C163" t="inlineStr">
         <is>
-          <t>Advertising and promotion</t>
+          <t>Basic and diluted loss per common share</t>
         </is>
       </c>
       <c r="D163" t="inlineStr">
         <is>
-          <t>OtherOperatingExpenses</t>
-        </is>
-      </c>
-      <c r="E163" s="5" t="n">
-        <v>0.004416</v>
+          <t>BasicEPS</t>
+        </is>
+      </c>
+      <c r="E163" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="F163" t="inlineStr">
         <is>
@@ -11351,15 +11371,11 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I163" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J163" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="I163" s="5" t="n">
+        <v>-1.3e-07</v>
+      </c>
+      <c r="J163" s="5" t="n">
+        <v>-1.1e-07</v>
       </c>
     </row>
     <row r="164">
@@ -11370,20 +11386,24 @@
       </c>
       <c r="B164" t="inlineStr">
         <is>
-          <t>Expenses</t>
+          <t>Other income (expenses)</t>
         </is>
       </c>
       <c r="C164" t="inlineStr">
         <is>
-          <t>Amortization of capital assets</t>
+          <t>Basic and diluted weighted average number</t>
         </is>
       </c>
       <c r="D164" t="inlineStr"/>
-      <c r="E164" s="5" t="n">
-        <v>0.010505</v>
-      </c>
-      <c r="F164" s="5" t="n">
-        <v>0.00019</v>
+      <c r="E164" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F164" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="G164" t="inlineStr">
         <is>
@@ -11395,15 +11415,11 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I164" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J164" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="I164" s="5" t="n">
+        <v>60.245282</v>
+      </c>
+      <c r="J164" s="5" t="n">
+        <v>93.10255100000001</v>
       </c>
     </row>
     <row r="165">
@@ -11414,24 +11430,24 @@
       </c>
       <c r="B165" t="inlineStr">
         <is>
-          <t>Expenses</t>
+          <t>Other comprehensive income (loss)</t>
         </is>
       </c>
       <c r="C165" t="inlineStr">
         <is>
-          <t>Bank charges</t>
-        </is>
-      </c>
-      <c r="D165" t="inlineStr">
-        <is>
-          <t>SellingGeneralAndAdministration</t>
-        </is>
-      </c>
-      <c r="E165" s="5" t="n">
-        <v>0.00246</v>
-      </c>
-      <c r="F165" s="5" t="n">
-        <v>0.001018</v>
+          <t>Foreign currency translation adjustment</t>
+        </is>
+      </c>
+      <c r="D165" t="inlineStr"/>
+      <c r="E165" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F165" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="G165" t="inlineStr">
         <is>
@@ -11448,10 +11464,8 @@
           <t>-</t>
         </is>
       </c>
-      <c r="J165" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="J165" s="5" t="n">
+        <v>-0.018059</v>
       </c>
     </row>
     <row r="166">
@@ -11462,24 +11476,28 @@
       </c>
       <c r="B166" t="inlineStr">
         <is>
-          <t>Expenses</t>
+          <t>Other comprehensive income (loss)</t>
         </is>
       </c>
       <c r="C166" t="inlineStr">
         <is>
-          <t>Office and miscellaneous</t>
+          <t>Net and comprehensive loss for the year $</t>
         </is>
       </c>
       <c r="D166" t="inlineStr">
         <is>
-          <t>SellingGeneralAndAdministration</t>
-        </is>
-      </c>
-      <c r="E166" s="5" t="n">
-        <v>0.049198</v>
-      </c>
-      <c r="F166" s="5" t="n">
-        <v>0.028105</v>
+          <t>NetIncome</t>
+        </is>
+      </c>
+      <c r="E166" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F166" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="G166" t="inlineStr">
         <is>
@@ -11491,15 +11509,11 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I166" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J166" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="I166" s="5" t="n">
+        <v>-7.738457</v>
+      </c>
+      <c r="J166" s="5" t="n">
+        <v>-10.603187</v>
       </c>
     </row>
     <row r="167">
@@ -11515,34 +11529,34 @@
       </c>
       <c r="C167" t="inlineStr">
         <is>
-          <t>Rent</t>
+          <t>Marketing (Note 8) $</t>
         </is>
       </c>
       <c r="D167" t="inlineStr">
         <is>
-          <t>SellingGeneralAndAdministration</t>
-        </is>
-      </c>
-      <c r="E167" s="5" t="n">
-        <v>0.01032</v>
-      </c>
-      <c r="F167" s="5" t="n">
-        <v>0.00229</v>
+          <t>OtherOperatingExpenses</t>
+        </is>
+      </c>
+      <c r="E167" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F167" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="G167" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="H167" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="I167" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="H167" s="5" t="n">
+        <v>0.458437</v>
+      </c>
+      <c r="I167" s="5" t="n">
+        <v>0.86105</v>
       </c>
       <c r="J167" t="inlineStr">
         <is>
@@ -11563,34 +11577,34 @@
       </c>
       <c r="C168" t="inlineStr">
         <is>
-          <t>Salaries and benefits</t>
+          <t>Management fees (Note 8)</t>
         </is>
       </c>
       <c r="D168" t="inlineStr">
         <is>
-          <t>OtherOperatingExpenses</t>
-        </is>
-      </c>
-      <c r="E168" s="5" t="n">
-        <v>0.29766</v>
-      </c>
-      <c r="F168" s="5" t="n">
-        <v>0.013229</v>
+          <t>SellingGeneralAndAdministration</t>
+        </is>
+      </c>
+      <c r="E168" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F168" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="G168" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="H168" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="I168" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="H168" s="5" t="n">
+        <v>0.1795</v>
+      </c>
+      <c r="I168" s="5" t="n">
+        <v>0.686685</v>
       </c>
       <c r="J168" t="inlineStr">
         <is>
@@ -11611,12 +11625,18 @@
       </c>
       <c r="C169" t="inlineStr">
         <is>
-          <t>Subcontractors</t>
-        </is>
-      </c>
-      <c r="D169" t="inlineStr"/>
-      <c r="E169" s="5" t="n">
-        <v>0.489658</v>
+          <t>Total expense</t>
+        </is>
+      </c>
+      <c r="D169" t="inlineStr">
+        <is>
+          <t>OperatingExpense</t>
+        </is>
+      </c>
+      <c r="E169" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="F169" t="inlineStr">
         <is>
@@ -11628,15 +11648,11 @@
           <t>-</t>
         </is>
       </c>
-      <c r="H169" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="I169" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="H169" s="5" t="n">
+        <v>1.031904</v>
+      </c>
+      <c r="I169" s="5" t="n">
+        <v>2.596099</v>
       </c>
       <c r="J169" t="inlineStr">
         <is>
@@ -11652,35 +11668,37 @@
       </c>
       <c r="B170" t="inlineStr">
         <is>
-          <t>Expenses</t>
+          <t>Other income</t>
         </is>
       </c>
       <c r="C170" t="inlineStr">
         <is>
-          <t>Telecommunications</t>
-        </is>
-      </c>
-      <c r="D170" t="inlineStr"/>
-      <c r="E170" s="5" t="n">
-        <v>0.007335</v>
-      </c>
-      <c r="F170" s="5" t="n">
-        <v>0.000187</v>
-      </c>
-      <c r="G170" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H170" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="I170" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>Interest income</t>
+        </is>
+      </c>
+      <c r="D170" t="inlineStr">
+        <is>
+          <t>InterestIncomeNonOperating</t>
+        </is>
+      </c>
+      <c r="E170" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F170" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G170" s="5" t="n">
+        <v>0.016903</v>
+      </c>
+      <c r="H170" s="5" t="n">
+        <v>0.04075</v>
+      </c>
+      <c r="I170" s="5" t="n">
+        <v>0.228167</v>
       </c>
       <c r="J170" t="inlineStr">
         <is>
@@ -11696,17 +11714,19 @@
       </c>
       <c r="B171" t="inlineStr">
         <is>
-          <t>Expenses</t>
+          <t>Other income</t>
         </is>
       </c>
       <c r="C171" t="inlineStr">
         <is>
-          <t>Travel and lodging</t>
+          <t>Foreign currency exchange gain (loss)</t>
         </is>
       </c>
       <c r="D171" t="inlineStr"/>
-      <c r="E171" s="5" t="n">
-        <v>0.001183</v>
+      <c r="E171" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="F171" t="inlineStr">
         <is>
@@ -11723,10 +11743,8 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I171" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="I171" s="5" t="n">
+        <v>-0.005925</v>
       </c>
       <c r="J171" t="inlineStr">
         <is>
@@ -11742,39 +11760,33 @@
       </c>
       <c r="B172" t="inlineStr">
         <is>
-          <t>Expenses</t>
+          <t>Other income</t>
         </is>
       </c>
       <c r="C172" t="inlineStr">
         <is>
-          <t>Loss before other items and income taxes</t>
-        </is>
-      </c>
-      <c r="D172" t="inlineStr">
-        <is>
-          <t>TaxProvision</t>
-        </is>
-      </c>
-      <c r="E172" s="5" t="n">
-        <v>-0.386243</v>
-      </c>
-      <c r="F172" s="5" t="n">
-        <v>-0.09699000000000001</v>
-      </c>
-      <c r="G172" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H172" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="I172" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>Share based compensation</t>
+        </is>
+      </c>
+      <c r="D172" t="inlineStr"/>
+      <c r="E172" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F172" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G172" s="5" t="n">
+        <v>-0.0324</v>
+      </c>
+      <c r="H172" s="5" t="n">
+        <v>-0.8711</v>
+      </c>
+      <c r="I172" s="5" t="n">
+        <v>-5.3646</v>
       </c>
       <c r="J172" t="inlineStr">
         <is>
@@ -11790,37 +11802,37 @@
       </c>
       <c r="B173" t="inlineStr">
         <is>
-          <t>Other items</t>
+          <t>Other income</t>
         </is>
       </c>
       <c r="C173" t="inlineStr">
         <is>
-          <t>Damages paid on settlement of lawsuit (Note 12)</t>
-        </is>
-      </c>
-      <c r="D173" t="inlineStr"/>
-      <c r="E173" s="5" t="n">
-        <v>0.055</v>
+          <t>Net and comprehensive loss for the year $</t>
+        </is>
+      </c>
+      <c r="D173" t="inlineStr">
+        <is>
+          <t>NetIncome</t>
+        </is>
+      </c>
+      <c r="E173" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="F173" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="G173" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H173" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="I173" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="G173" s="5" t="n">
+        <v>-0.485772</v>
+      </c>
+      <c r="H173" s="5" t="n">
+        <v>-1.862254</v>
+      </c>
+      <c r="I173" s="5" t="n">
+        <v>-7.738457</v>
       </c>
       <c r="J173" t="inlineStr">
         <is>
@@ -11836,37 +11848,37 @@
       </c>
       <c r="B174" t="inlineStr">
         <is>
-          <t>Other items</t>
+          <t>Other income</t>
         </is>
       </c>
       <c r="C174" t="inlineStr">
         <is>
-          <t>Loss on disposal of capital assets</t>
-        </is>
-      </c>
-      <c r="D174" t="inlineStr"/>
-      <c r="E174" s="5" t="n">
-        <v>0.007385</v>
+          <t>Basic and diluted loss per common share $</t>
+        </is>
+      </c>
+      <c r="D174" t="inlineStr">
+        <is>
+          <t>BasicEPS</t>
+        </is>
+      </c>
+      <c r="E174" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="F174" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="G174" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H174" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="I174" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="G174" s="5" t="n">
+        <v>-2e-08</v>
+      </c>
+      <c r="H174" s="5" t="n">
+        <v>-5.999999999999999e-08</v>
+      </c>
+      <c r="I174" s="5" t="n">
+        <v>-1.3e-07</v>
       </c>
       <c r="J174" t="inlineStr">
         <is>
@@ -11882,41 +11894,37 @@
       </c>
       <c r="B175" t="inlineStr">
         <is>
-          <t>Other items</t>
+          <t>Basic and diluted weighted average</t>
         </is>
       </c>
       <c r="C175" t="inlineStr">
         <is>
-          <t>Interest income</t>
+          <t>Basic and diluted weighted average number of common shares outstanding</t>
         </is>
       </c>
       <c r="D175" t="inlineStr">
         <is>
-          <t>InterestIncomeNonOperating</t>
-        </is>
-      </c>
-      <c r="E175" s="5" t="n">
-        <v>-0.026375</v>
+          <t>SharesOutstanding</t>
+        </is>
+      </c>
+      <c r="E175" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="F175" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="G175" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H175" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="I175" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="G175" s="5" t="n">
+        <v>26.217</v>
+      </c>
+      <c r="H175" s="5" t="n">
+        <v>33.852304</v>
+      </c>
+      <c r="I175" s="5" t="n">
+        <v>60.245282</v>
       </c>
       <c r="J175" t="inlineStr">
         <is>
@@ -11932,32 +11940,34 @@
       </c>
       <c r="B176" t="inlineStr">
         <is>
-          <t>Other items</t>
+          <t>Expenses</t>
         </is>
       </c>
       <c r="C176" t="inlineStr">
         <is>
-          <t>Write down of equipment held for sale</t>
-        </is>
-      </c>
-      <c r="D176" t="inlineStr"/>
+          <t>Advertising and promotion $</t>
+        </is>
+      </c>
+      <c r="D176" t="inlineStr">
+        <is>
+          <t>OtherOperatingExpenses</t>
+        </is>
+      </c>
       <c r="E176" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="F176" s="5" t="n">
-        <v>0.009058999999999999</v>
-      </c>
-      <c r="G176" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H176" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="F176" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G176" s="5" t="n">
+        <v>0.208018</v>
+      </c>
+      <c r="H176" s="5" t="n">
+        <v>0.458437</v>
       </c>
       <c r="I176" t="inlineStr">
         <is>
@@ -11978,30 +11988,34 @@
       </c>
       <c r="B177" t="inlineStr">
         <is>
-          <t>Other items</t>
+          <t>Expenses</t>
         </is>
       </c>
       <c r="C177" t="inlineStr">
         <is>
-          <t>Other items total</t>
-        </is>
-      </c>
-      <c r="D177" t="inlineStr"/>
-      <c r="E177" s="5" t="n">
-        <v>0.03601</v>
-      </c>
-      <c r="F177" s="5" t="n">
-        <v>0.009058999999999999</v>
-      </c>
-      <c r="G177" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H177" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>Management fees</t>
+        </is>
+      </c>
+      <c r="D177" t="inlineStr">
+        <is>
+          <t>SellingGeneralAndAdministration</t>
+        </is>
+      </c>
+      <c r="E177" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F177" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G177" s="5" t="n">
+        <v>0.204</v>
+      </c>
+      <c r="H177" s="5" t="n">
+        <v>0.1795</v>
       </c>
       <c r="I177" t="inlineStr">
         <is>
@@ -12022,29 +12036,27 @@
       </c>
       <c r="B178" t="inlineStr">
         <is>
-          <t>Other items</t>
+          <t>Expenses</t>
         </is>
       </c>
       <c r="C178" t="inlineStr">
         <is>
-          <t>Loss before income taxes</t>
-        </is>
-      </c>
-      <c r="D178" t="inlineStr">
-        <is>
-          <t>PretaxIncome</t>
-        </is>
-      </c>
-      <c r="E178" s="5" t="n">
-        <v>-0.422253</v>
-      </c>
-      <c r="F178" s="5" t="n">
-        <v>-0.106049</v>
-      </c>
-      <c r="G178" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>Project evaluation</t>
+        </is>
+      </c>
+      <c r="D178" t="inlineStr"/>
+      <c r="E178" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F178" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G178" s="5" t="n">
+        <v>0.034361</v>
       </c>
       <c r="H178" t="inlineStr">
         <is>
@@ -12070,27 +12082,27 @@
       </c>
       <c r="B179" t="inlineStr">
         <is>
-          <t>Income taxes</t>
+          <t>Other income</t>
         </is>
       </c>
       <c r="C179" t="inlineStr">
         <is>
-          <t>Current</t>
+          <t>Settlement of flow-through liability</t>
         </is>
       </c>
       <c r="D179" t="inlineStr"/>
-      <c r="E179" s="5" t="n">
-        <v>0.000175</v>
+      <c r="E179" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="F179" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="G179" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="G179" s="5" t="n">
+        <v>0.1848</v>
       </c>
       <c r="H179" t="inlineStr">
         <is>
@@ -12114,14 +12126,10 @@
           <t>income_statement</t>
         </is>
       </c>
-      <c r="B180" t="inlineStr">
-        <is>
-          <t>Income taxes</t>
-        </is>
-      </c>
+      <c r="B180" t="inlineStr"/>
       <c r="C180" t="inlineStr">
         <is>
-          <t>Future</t>
+          <t>For the years ended August 31 August</t>
         </is>
       </c>
       <c r="D180" t="inlineStr"/>
@@ -12135,10 +12143,8 @@
           <t>-</t>
         </is>
       </c>
-      <c r="G180" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="G180" s="5" t="n">
+        <v>3.1e-05</v>
       </c>
       <c r="H180" t="inlineStr">
         <is>
@@ -12164,27 +12170,31 @@
       </c>
       <c r="B181" t="inlineStr">
         <is>
-          <t>Income taxes</t>
+          <t>Operating expenses</t>
         </is>
       </c>
       <c r="C181" t="inlineStr">
         <is>
-          <t>Income taxes total</t>
-        </is>
-      </c>
-      <c r="D181" t="inlineStr"/>
-      <c r="E181" s="5" t="n">
-        <v>0.000175</v>
+          <t>Advertising and promotion (note 8) $ 208,018 $</t>
+        </is>
+      </c>
+      <c r="D181" t="inlineStr">
+        <is>
+          <t>OtherOperatingExpenses</t>
+        </is>
+      </c>
+      <c r="E181" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="F181" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="G181" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="G181" s="5" t="n">
+        <v>0.109464</v>
       </c>
       <c r="H181" t="inlineStr">
         <is>
@@ -12210,29 +12220,31 @@
       </c>
       <c r="B182" t="inlineStr">
         <is>
-          <t>Income taxes</t>
+          <t>Operating expenses</t>
         </is>
       </c>
       <c r="C182" t="inlineStr">
         <is>
-          <t>Net loss and comprehensive loss for the year</t>
+          <t>General and administrative 85,110</t>
         </is>
       </c>
       <c r="D182" t="inlineStr">
         <is>
-          <t>NetIncome</t>
-        </is>
-      </c>
-      <c r="E182" s="5" t="n">
-        <v>-0.422428</v>
-      </c>
-      <c r="F182" s="5" t="n">
-        <v>-0.106049</v>
-      </c>
-      <c r="G182" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>GeneralAndAdministrativeExpense</t>
+        </is>
+      </c>
+      <c r="E182" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F182" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G182" s="5" t="n">
+        <v>0.030303</v>
       </c>
       <c r="H182" t="inlineStr">
         <is>
@@ -12258,29 +12270,31 @@
       </c>
       <c r="B183" t="inlineStr">
         <is>
-          <t>Net loss per share</t>
+          <t>Operating expenses</t>
         </is>
       </c>
       <c r="C183" t="inlineStr">
         <is>
-          <t>Basic and diluted</t>
+          <t>Management fees (note 8) 204,000</t>
         </is>
       </c>
       <c r="D183" t="inlineStr">
         <is>
-          <t>BasicEPS</t>
-        </is>
-      </c>
-      <c r="E183" s="5" t="n">
-        <v>-2.1e-08</v>
-      </c>
-      <c r="F183" s="5" t="n">
-        <v>-5e-09</v>
-      </c>
-      <c r="G183" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>SellingGeneralAndAdministration</t>
+        </is>
+      </c>
+      <c r="E183" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F183" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G183" s="5" t="n">
+        <v>0.1186</v>
       </c>
       <c r="H183" t="inlineStr">
         <is>
@@ -12306,25 +12320,31 @@
       </c>
       <c r="B184" t="inlineStr">
         <is>
-          <t>Weighted average number of common shares outstanding (000's)</t>
+          <t>Operating expenses</t>
         </is>
       </c>
       <c r="C184" t="inlineStr">
         <is>
-          <t>Basic and diluted</t>
-        </is>
-      </c>
-      <c r="D184" t="inlineStr"/>
-      <c r="E184" s="5" t="n">
-        <v>0.019742</v>
-      </c>
-      <c r="F184" s="5" t="n">
-        <v>0.019742</v>
-      </c>
-      <c r="G184" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>Professional fees 100,633</t>
+        </is>
+      </c>
+      <c r="D184" t="inlineStr">
+        <is>
+          <t>ProfessionalExpenseAndContractServicesExpense</t>
+        </is>
+      </c>
+      <c r="E184" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F184" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G184" s="5" t="n">
+        <v>0.257592</v>
       </c>
       <c r="H184" t="inlineStr">
         <is>
@@ -12350,20 +12370,24 @@
       </c>
       <c r="B185" t="inlineStr">
         <is>
-          <t>#           $             (deficit)      (deficiency)</t>
+          <t>Operating expenses</t>
         </is>
       </c>
       <c r="C185" t="inlineStr">
         <is>
-          <t>Balance - August 31, 2007 19,742,200 $2,637,940</t>
+          <t>Project evaluation 34,361</t>
         </is>
       </c>
       <c r="D185" t="inlineStr"/>
-      <c r="E185" s="5" t="n">
-        <v>1.678195</v>
-      </c>
-      <c r="F185" s="5" t="n">
-        <v>-0.959745</v>
+      <c r="E185" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F185" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="G185" t="inlineStr">
         <is>
@@ -12394,12 +12418,12 @@
       </c>
       <c r="B186" t="inlineStr">
         <is>
-          <t>#           $             (deficit)      (deficiency)</t>
+          <t>Operating expenses</t>
         </is>
       </c>
       <c r="C186" t="inlineStr">
         <is>
-          <t>Reduction of stated capital (Note 6) - (2,636,940)</t>
+          <t>Regulatory and filing fees 22,953</t>
         </is>
       </c>
       <c r="D186" t="inlineStr"/>
@@ -12408,13 +12432,13 @@
           <t>-</t>
         </is>
       </c>
-      <c r="F186" s="5" t="n">
-        <v>2.63694</v>
-      </c>
-      <c r="G186" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="F186" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G186" s="5" t="n">
+        <v>0.039531</v>
       </c>
       <c r="H186" t="inlineStr">
         <is>
@@ -12440,25 +12464,31 @@
       </c>
       <c r="B187" t="inlineStr">
         <is>
-          <t>#           $             (deficit)      (deficiency)</t>
+          <t>Operating expenses</t>
         </is>
       </c>
       <c r="C187" t="inlineStr">
         <is>
-          <t>Dividends paid (Note 6) - -</t>
-        </is>
-      </c>
-      <c r="D187" t="inlineStr"/>
-      <c r="E187" s="5" t="n">
-        <v>-1.211184</v>
-      </c>
-      <c r="F187" s="5" t="n">
-        <v>-1.211184</v>
-      </c>
-      <c r="G187" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>Operating expenses total</t>
+        </is>
+      </c>
+      <c r="D187" t="inlineStr">
+        <is>
+          <t>OperatingExpense</t>
+        </is>
+      </c>
+      <c r="E187" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F187" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G187" s="5" t="n">
+        <v>0.55549</v>
       </c>
       <c r="H187" t="inlineStr">
         <is>
@@ -12484,29 +12514,31 @@
       </c>
       <c r="B188" t="inlineStr">
         <is>
-          <t>#           $             (deficit)      (deficiency)</t>
+          <t>Other income (expense)</t>
         </is>
       </c>
       <c r="C188" t="inlineStr">
         <is>
-          <t>Net loss for the year - -</t>
+          <t>Interest income 16,903</t>
         </is>
       </c>
       <c r="D188" t="inlineStr">
         <is>
-          <t>NetIncome</t>
-        </is>
-      </c>
-      <c r="E188" s="5" t="n">
-        <v>-0.422428</v>
-      </c>
-      <c r="F188" s="5" t="n">
-        <v>-0.422428</v>
-      </c>
-      <c r="G188" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>InterestIncomeNonOperating</t>
+        </is>
+      </c>
+      <c r="E188" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F188" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G188" s="5" t="n">
+        <v>0.009782000000000001</v>
       </c>
       <c r="H188" t="inlineStr">
         <is>
@@ -12532,25 +12564,27 @@
       </c>
       <c r="B189" t="inlineStr">
         <is>
-          <t>#           $             (deficit)      (deficiency)</t>
+          <t>Other income (expense)</t>
         </is>
       </c>
       <c r="C189" t="inlineStr">
         <is>
-          <t>Balance - August 31, 2008 19,742,200 $1,000</t>
+          <t>Settlement of flow-through liability (note 6) 184,800</t>
         </is>
       </c>
       <c r="D189" t="inlineStr"/>
-      <c r="E189" s="5" t="n">
-        <v>0.044583</v>
-      </c>
-      <c r="F189" s="5" t="n">
-        <v>0.043583</v>
-      </c>
-      <c r="G189" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="E189" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F189" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G189" s="5" t="n">
+        <v>0.07920000000000001</v>
       </c>
       <c r="H189" t="inlineStr">
         <is>
@@ -12576,37 +12610,1525 @@
       </c>
       <c r="B190" t="inlineStr">
         <is>
+          <t>Other income (expense)</t>
+        </is>
+      </c>
+      <c r="C190" t="inlineStr">
+        <is>
+          <t>Share-based compensation (note 6) (32,400)</t>
+        </is>
+      </c>
+      <c r="D190" t="inlineStr"/>
+      <c r="E190" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F190" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G190" s="5" t="n">
+        <v>-0.43475</v>
+      </c>
+      <c r="H190" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I190" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J190" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="191">
+      <c r="A191" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B191" t="inlineStr">
+        <is>
+          <t>Other income (expense)</t>
+        </is>
+      </c>
+      <c r="C191" t="inlineStr">
+        <is>
+          <t>Net and comprehensive loss for the year $ (485,772) $</t>
+        </is>
+      </c>
+      <c r="D191" t="inlineStr"/>
+      <c r="E191" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F191" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G191" s="5" t="n">
+        <v>-0.901258</v>
+      </c>
+      <c r="H191" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I191" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J191" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="192">
+      <c r="A192" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B192" t="inlineStr">
+        <is>
+          <t>Other income (expense)</t>
+        </is>
+      </c>
+      <c r="C192" t="inlineStr">
+        <is>
+          <t>Basic and diluted loss per common share $ (0.02) $</t>
+        </is>
+      </c>
+      <c r="D192" t="inlineStr"/>
+      <c r="E192" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F192" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G192" s="5" t="n">
+        <v>-5.999999999999999e-08</v>
+      </c>
+      <c r="H192" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I192" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J192" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="193">
+      <c r="A193" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B193" t="inlineStr">
+        <is>
+          <t>Basic and diluted weighted average</t>
+        </is>
+      </c>
+      <c r="C193" t="inlineStr">
+        <is>
+          <t>Basic and diluted weighted average number of common shares outstanding 26,217,000</t>
+        </is>
+      </c>
+      <c r="D193" t="inlineStr">
+        <is>
+          <t>SharesOutstanding</t>
+        </is>
+      </c>
+      <c r="E193" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F193" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G193" s="5" t="n">
+        <v>14.234244</v>
+      </c>
+      <c r="H193" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I193" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J193" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="194">
+      <c r="A194" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B194" t="inlineStr"/>
+      <c r="C194" t="inlineStr">
+        <is>
+          <t>Revenue</t>
+        </is>
+      </c>
+      <c r="D194" t="inlineStr">
+        <is>
+          <t>TotalRevenue</t>
+        </is>
+      </c>
+      <c r="E194" s="5" t="n">
+        <v>0.633741</v>
+      </c>
+      <c r="F194" s="5" t="n">
+        <v>6.999999999999999e-05</v>
+      </c>
+      <c r="G194" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H194" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I194" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J194" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="195">
+      <c r="A195" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B195" t="inlineStr">
+        <is>
+          <t>Expenses</t>
+        </is>
+      </c>
+      <c r="C195" t="inlineStr">
+        <is>
+          <t>Advertising and promotion</t>
+        </is>
+      </c>
+      <c r="D195" t="inlineStr">
+        <is>
+          <t>OtherOperatingExpenses</t>
+        </is>
+      </c>
+      <c r="E195" s="5" t="n">
+        <v>0.004416</v>
+      </c>
+      <c r="F195" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G195" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H195" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I195" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J195" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="196">
+      <c r="A196" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B196" t="inlineStr">
+        <is>
+          <t>Expenses</t>
+        </is>
+      </c>
+      <c r="C196" t="inlineStr">
+        <is>
+          <t>Amortization of capital assets</t>
+        </is>
+      </c>
+      <c r="D196" t="inlineStr"/>
+      <c r="E196" s="5" t="n">
+        <v>0.010505</v>
+      </c>
+      <c r="F196" s="5" t="n">
+        <v>0.00019</v>
+      </c>
+      <c r="G196" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H196" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I196" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J196" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="197">
+      <c r="A197" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B197" t="inlineStr">
+        <is>
+          <t>Expenses</t>
+        </is>
+      </c>
+      <c r="C197" t="inlineStr">
+        <is>
+          <t>Bank charges</t>
+        </is>
+      </c>
+      <c r="D197" t="inlineStr">
+        <is>
+          <t>SellingGeneralAndAdministration</t>
+        </is>
+      </c>
+      <c r="E197" s="5" t="n">
+        <v>0.00246</v>
+      </c>
+      <c r="F197" s="5" t="n">
+        <v>0.001018</v>
+      </c>
+      <c r="G197" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H197" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I197" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J197" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="198">
+      <c r="A198" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B198" t="inlineStr">
+        <is>
+          <t>Expenses</t>
+        </is>
+      </c>
+      <c r="C198" t="inlineStr">
+        <is>
+          <t>Office and miscellaneous</t>
+        </is>
+      </c>
+      <c r="D198" t="inlineStr">
+        <is>
+          <t>SellingGeneralAndAdministration</t>
+        </is>
+      </c>
+      <c r="E198" s="5" t="n">
+        <v>0.049198</v>
+      </c>
+      <c r="F198" s="5" t="n">
+        <v>0.028105</v>
+      </c>
+      <c r="G198" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H198" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I198" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J198" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="199">
+      <c r="A199" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B199" t="inlineStr">
+        <is>
+          <t>Expenses</t>
+        </is>
+      </c>
+      <c r="C199" t="inlineStr">
+        <is>
+          <t>Rent</t>
+        </is>
+      </c>
+      <c r="D199" t="inlineStr">
+        <is>
+          <t>SellingGeneralAndAdministration</t>
+        </is>
+      </c>
+      <c r="E199" s="5" t="n">
+        <v>0.01032</v>
+      </c>
+      <c r="F199" s="5" t="n">
+        <v>0.00229</v>
+      </c>
+      <c r="G199" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H199" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I199" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J199" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="200">
+      <c r="A200" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B200" t="inlineStr">
+        <is>
+          <t>Expenses</t>
+        </is>
+      </c>
+      <c r="C200" t="inlineStr">
+        <is>
+          <t>Salaries and benefits</t>
+        </is>
+      </c>
+      <c r="D200" t="inlineStr">
+        <is>
+          <t>OtherOperatingExpenses</t>
+        </is>
+      </c>
+      <c r="E200" s="5" t="n">
+        <v>0.29766</v>
+      </c>
+      <c r="F200" s="5" t="n">
+        <v>0.013229</v>
+      </c>
+      <c r="G200" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H200" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I200" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J200" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="201">
+      <c r="A201" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B201" t="inlineStr">
+        <is>
+          <t>Expenses</t>
+        </is>
+      </c>
+      <c r="C201" t="inlineStr">
+        <is>
+          <t>Subcontractors</t>
+        </is>
+      </c>
+      <c r="D201" t="inlineStr"/>
+      <c r="E201" s="5" t="n">
+        <v>0.489658</v>
+      </c>
+      <c r="F201" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G201" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H201" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I201" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J201" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="202">
+      <c r="A202" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B202" t="inlineStr">
+        <is>
+          <t>Expenses</t>
+        </is>
+      </c>
+      <c r="C202" t="inlineStr">
+        <is>
+          <t>Telecommunications</t>
+        </is>
+      </c>
+      <c r="D202" t="inlineStr"/>
+      <c r="E202" s="5" t="n">
+        <v>0.007335</v>
+      </c>
+      <c r="F202" s="5" t="n">
+        <v>0.000187</v>
+      </c>
+      <c r="G202" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H202" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I202" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J202" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="203">
+      <c r="A203" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B203" t="inlineStr">
+        <is>
+          <t>Expenses</t>
+        </is>
+      </c>
+      <c r="C203" t="inlineStr">
+        <is>
+          <t>Travel and lodging</t>
+        </is>
+      </c>
+      <c r="D203" t="inlineStr"/>
+      <c r="E203" s="5" t="n">
+        <v>0.001183</v>
+      </c>
+      <c r="F203" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G203" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H203" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I203" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J203" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="204">
+      <c r="A204" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B204" t="inlineStr">
+        <is>
+          <t>Expenses</t>
+        </is>
+      </c>
+      <c r="C204" t="inlineStr">
+        <is>
+          <t>Loss before other items and income taxes</t>
+        </is>
+      </c>
+      <c r="D204" t="inlineStr">
+        <is>
+          <t>TaxProvision</t>
+        </is>
+      </c>
+      <c r="E204" s="5" t="n">
+        <v>-0.386243</v>
+      </c>
+      <c r="F204" s="5" t="n">
+        <v>-0.09699000000000001</v>
+      </c>
+      <c r="G204" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H204" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I204" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J204" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="205">
+      <c r="A205" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B205" t="inlineStr">
+        <is>
+          <t>Other items</t>
+        </is>
+      </c>
+      <c r="C205" t="inlineStr">
+        <is>
+          <t>Damages paid on settlement of lawsuit (Note 12)</t>
+        </is>
+      </c>
+      <c r="D205" t="inlineStr"/>
+      <c r="E205" s="5" t="n">
+        <v>0.055</v>
+      </c>
+      <c r="F205" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G205" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H205" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I205" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J205" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="206">
+      <c r="A206" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B206" t="inlineStr">
+        <is>
+          <t>Other items</t>
+        </is>
+      </c>
+      <c r="C206" t="inlineStr">
+        <is>
+          <t>Loss on disposal of capital assets</t>
+        </is>
+      </c>
+      <c r="D206" t="inlineStr"/>
+      <c r="E206" s="5" t="n">
+        <v>0.007385</v>
+      </c>
+      <c r="F206" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G206" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H206" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I206" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J206" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="207">
+      <c r="A207" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B207" t="inlineStr">
+        <is>
+          <t>Other items</t>
+        </is>
+      </c>
+      <c r="C207" t="inlineStr">
+        <is>
+          <t>Interest income</t>
+        </is>
+      </c>
+      <c r="D207" t="inlineStr">
+        <is>
+          <t>InterestIncomeNonOperating</t>
+        </is>
+      </c>
+      <c r="E207" s="5" t="n">
+        <v>-0.026375</v>
+      </c>
+      <c r="F207" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G207" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H207" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I207" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J207" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="208">
+      <c r="A208" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B208" t="inlineStr">
+        <is>
+          <t>Other items</t>
+        </is>
+      </c>
+      <c r="C208" t="inlineStr">
+        <is>
+          <t>Write down of equipment held for sale</t>
+        </is>
+      </c>
+      <c r="D208" t="inlineStr"/>
+      <c r="E208" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F208" s="5" t="n">
+        <v>0.009058999999999999</v>
+      </c>
+      <c r="G208" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H208" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I208" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J208" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="209">
+      <c r="A209" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B209" t="inlineStr">
+        <is>
+          <t>Other items</t>
+        </is>
+      </c>
+      <c r="C209" t="inlineStr">
+        <is>
+          <t>Other items total</t>
+        </is>
+      </c>
+      <c r="D209" t="inlineStr"/>
+      <c r="E209" s="5" t="n">
+        <v>0.03601</v>
+      </c>
+      <c r="F209" s="5" t="n">
+        <v>0.009058999999999999</v>
+      </c>
+      <c r="G209" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H209" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I209" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J209" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="210">
+      <c r="A210" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B210" t="inlineStr">
+        <is>
+          <t>Other items</t>
+        </is>
+      </c>
+      <c r="C210" t="inlineStr">
+        <is>
+          <t>Loss before income taxes</t>
+        </is>
+      </c>
+      <c r="D210" t="inlineStr">
+        <is>
+          <t>PretaxIncome</t>
+        </is>
+      </c>
+      <c r="E210" s="5" t="n">
+        <v>-0.422253</v>
+      </c>
+      <c r="F210" s="5" t="n">
+        <v>-0.106049</v>
+      </c>
+      <c r="G210" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H210" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I210" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J210" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="211">
+      <c r="A211" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B211" t="inlineStr">
+        <is>
+          <t>Income taxes</t>
+        </is>
+      </c>
+      <c r="C211" t="inlineStr">
+        <is>
+          <t>Current</t>
+        </is>
+      </c>
+      <c r="D211" t="inlineStr"/>
+      <c r="E211" s="5" t="n">
+        <v>0.000175</v>
+      </c>
+      <c r="F211" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G211" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H211" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I211" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J211" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="212">
+      <c r="A212" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B212" t="inlineStr">
+        <is>
+          <t>Income taxes</t>
+        </is>
+      </c>
+      <c r="C212" t="inlineStr">
+        <is>
+          <t>Future</t>
+        </is>
+      </c>
+      <c r="D212" t="inlineStr"/>
+      <c r="E212" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F212" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G212" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H212" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I212" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J212" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="213">
+      <c r="A213" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B213" t="inlineStr">
+        <is>
+          <t>Income taxes</t>
+        </is>
+      </c>
+      <c r="C213" t="inlineStr">
+        <is>
+          <t>Income taxes total</t>
+        </is>
+      </c>
+      <c r="D213" t="inlineStr"/>
+      <c r="E213" s="5" t="n">
+        <v>0.000175</v>
+      </c>
+      <c r="F213" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G213" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H213" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I213" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J213" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="214">
+      <c r="A214" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B214" t="inlineStr">
+        <is>
+          <t>Income taxes</t>
+        </is>
+      </c>
+      <c r="C214" t="inlineStr">
+        <is>
+          <t>Net loss and comprehensive loss for the year</t>
+        </is>
+      </c>
+      <c r="D214" t="inlineStr">
+        <is>
+          <t>NetIncome</t>
+        </is>
+      </c>
+      <c r="E214" s="5" t="n">
+        <v>-0.422428</v>
+      </c>
+      <c r="F214" s="5" t="n">
+        <v>-0.106049</v>
+      </c>
+      <c r="G214" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H214" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I214" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J214" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="215">
+      <c r="A215" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B215" t="inlineStr">
+        <is>
+          <t>Net loss per share</t>
+        </is>
+      </c>
+      <c r="C215" t="inlineStr">
+        <is>
+          <t>Basic and diluted</t>
+        </is>
+      </c>
+      <c r="D215" t="inlineStr">
+        <is>
+          <t>BasicEPS</t>
+        </is>
+      </c>
+      <c r="E215" s="5" t="n">
+        <v>-2.1e-08</v>
+      </c>
+      <c r="F215" s="5" t="n">
+        <v>-5e-09</v>
+      </c>
+      <c r="G215" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H215" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I215" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J215" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="216">
+      <c r="A216" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B216" t="inlineStr">
+        <is>
+          <t>Weighted average number of common shares outstanding (000's)</t>
+        </is>
+      </c>
+      <c r="C216" t="inlineStr">
+        <is>
+          <t>Basic and diluted</t>
+        </is>
+      </c>
+      <c r="D216" t="inlineStr"/>
+      <c r="E216" s="5" t="n">
+        <v>0.019742</v>
+      </c>
+      <c r="F216" s="5" t="n">
+        <v>0.019742</v>
+      </c>
+      <c r="G216" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H216" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I216" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J216" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="217">
+      <c r="A217" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B217" t="inlineStr">
+        <is>
           <t>#           $             (deficit)      (deficiency)</t>
         </is>
       </c>
-      <c r="C190" t="inlineStr">
+      <c r="C217" t="inlineStr">
+        <is>
+          <t>Balance - August 31, 2007 19,742,200 $2,637,940</t>
+        </is>
+      </c>
+      <c r="D217" t="inlineStr"/>
+      <c r="E217" s="5" t="n">
+        <v>1.678195</v>
+      </c>
+      <c r="F217" s="5" t="n">
+        <v>-0.959745</v>
+      </c>
+      <c r="G217" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H217" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I217" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J217" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="218">
+      <c r="A218" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B218" t="inlineStr">
+        <is>
+          <t>#           $             (deficit)      (deficiency)</t>
+        </is>
+      </c>
+      <c r="C218" t="inlineStr">
+        <is>
+          <t>Reduction of stated capital (Note 6) - (2,636,940)</t>
+        </is>
+      </c>
+      <c r="D218" t="inlineStr"/>
+      <c r="E218" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F218" s="5" t="n">
+        <v>2.63694</v>
+      </c>
+      <c r="G218" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H218" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I218" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J218" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="219">
+      <c r="A219" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B219" t="inlineStr">
+        <is>
+          <t>#           $             (deficit)      (deficiency)</t>
+        </is>
+      </c>
+      <c r="C219" t="inlineStr">
+        <is>
+          <t>Dividends paid (Note 6) - -</t>
+        </is>
+      </c>
+      <c r="D219" t="inlineStr"/>
+      <c r="E219" s="5" t="n">
+        <v>-1.211184</v>
+      </c>
+      <c r="F219" s="5" t="n">
+        <v>-1.211184</v>
+      </c>
+      <c r="G219" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H219" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I219" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J219" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="220">
+      <c r="A220" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B220" t="inlineStr">
+        <is>
+          <t>#           $             (deficit)      (deficiency)</t>
+        </is>
+      </c>
+      <c r="C220" t="inlineStr">
+        <is>
+          <t>Net loss for the year - -</t>
+        </is>
+      </c>
+      <c r="D220" t="inlineStr">
+        <is>
+          <t>NetIncome</t>
+        </is>
+      </c>
+      <c r="E220" s="5" t="n">
+        <v>-0.422428</v>
+      </c>
+      <c r="F220" s="5" t="n">
+        <v>-0.422428</v>
+      </c>
+      <c r="G220" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H220" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I220" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J220" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="221">
+      <c r="A221" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B221" t="inlineStr">
+        <is>
+          <t>#           $             (deficit)      (deficiency)</t>
+        </is>
+      </c>
+      <c r="C221" t="inlineStr">
+        <is>
+          <t>Balance - August 31, 2008 19,742,200 $1,000</t>
+        </is>
+      </c>
+      <c r="D221" t="inlineStr"/>
+      <c r="E221" s="5" t="n">
+        <v>0.044583</v>
+      </c>
+      <c r="F221" s="5" t="n">
+        <v>0.043583</v>
+      </c>
+      <c r="G221" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H221" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I221" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J221" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="222">
+      <c r="A222" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B222" t="inlineStr">
+        <is>
+          <t>#           $             (deficit)      (deficiency)</t>
+        </is>
+      </c>
+      <c r="C222" t="inlineStr">
         <is>
           <t>Balance - August 31, 2009 19,742,200 $1,000</t>
         </is>
       </c>
-      <c r="D190" t="inlineStr"/>
-      <c r="E190" s="5" t="n">
+      <c r="D222" t="inlineStr"/>
+      <c r="E222" s="5" t="n">
         <v>-0.061466</v>
       </c>
-      <c r="F190" s="5" t="n">
+      <c r="F222" s="5" t="n">
         <v>-0.062466</v>
       </c>
-      <c r="G190" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H190" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="I190" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J190" t="inlineStr">
+      <c r="G222" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H222" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I222" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J222" t="inlineStr">
         <is>
           <t>-</t>
         </is>
